--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/15,09,26 ПОКОМ КИ/дв 15,09,26 млрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\15,09,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F24CEF1-4AA3-41C6-BBFB-E935FDB2ECD5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8A0E84-1D49-4ADD-9BF2-F0FF4180DC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AM$134</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -736,7 +728,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -753,8 +745,7 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -775,7 +766,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -7021,13 +7012,13 @@
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.42578125" customWidth="1"/>
     <col min="15" max="23" width="7" customWidth="1"/>
-    <col min="24" max="24" width="7" style="17" customWidth="1"/>
-    <col min="25" max="25" width="7.5703125" style="17" customWidth="1"/>
+    <col min="24" max="24" width="7" style="16" customWidth="1"/>
+    <col min="25" max="25" width="7.5703125" style="16" customWidth="1"/>
     <col min="26" max="27" width="5" customWidth="1"/>
     <col min="28" max="37" width="6" customWidth="1"/>
-    <col min="38" max="38" width="25.7109375" customWidth="1"/>
-    <col min="39" max="39" width="7" customWidth="1"/>
-    <col min="40" max="49" width="3" customWidth="1"/>
+    <col min="38" max="38" width="16.42578125" customWidth="1"/>
+    <col min="39" max="40" width="7" customWidth="1"/>
+    <col min="41" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -7053,7 +7044,7 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="18">
+      <c r="W1" s="17">
         <v>1</v>
       </c>
       <c r="X1" s="1"/>
@@ -7470,7 +7461,10 @@
         <f>SUM(AM6:AM499)</f>
         <v>8434</v>
       </c>
-      <c r="AN5" s="1"/>
+      <c r="AN5" s="4">
+        <f>SUM(AN6:AN499)</f>
+        <v>3439.5194000000006</v>
+      </c>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
@@ -7543,11 +7537,11 @@
         <f>X6</f>
         <v>300</v>
       </c>
-      <c r="X6" s="16">
+      <c r="X6" s="1">
         <f>VLOOKUP(A6,[1]Sheet!$A:$X,23,0)</f>
         <v>300</v>
       </c>
-      <c r="Y6" s="16" t="str">
+      <c r="Y6" s="1" t="str">
         <f>VLOOKUP(A6,[1]Sheet!$A:$X,24,0)</f>
         <v>Промо, сроки большие.</v>
       </c>
@@ -7594,7 +7588,10 @@
         <f>ROUND(G6*W6,0)</f>
         <v>300</v>
       </c>
-      <c r="AN6" s="1"/>
+      <c r="AN6" s="1">
+        <f>U6*G6</f>
+        <v>47.075599999999994</v>
+      </c>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1"/>
@@ -7662,8 +7659,8 @@
         <f>V7+U7*$W$1</f>
         <v>139.351</v>
       </c>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
       <c r="Z7" s="1">
         <f t="shared" ref="Z7:Z70" si="5">(F7+O7+P7+Q7+R7+S7+T7+W7)/U7</f>
         <v>12.344181240177681</v>
@@ -7707,7 +7704,10 @@
         <f t="shared" ref="AM7:AM70" si="6">ROUND(G7*W7,0)</f>
         <v>139</v>
       </c>
-      <c r="AN7" s="1"/>
+      <c r="AN7" s="1">
+        <f t="shared" ref="AN7:AN70" si="7">U7*G7</f>
+        <v>139.351</v>
+      </c>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
@@ -7775,8 +7775,8 @@
         <f>V8+U8*$W$1</f>
         <v>137.82639999999998</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
       <c r="Z8" s="1">
         <f t="shared" si="5"/>
         <v>12.448779043782615</v>
@@ -7820,7 +7820,10 @@
         <f t="shared" si="6"/>
         <v>138</v>
       </c>
-      <c r="AN8" s="1"/>
+      <c r="AN8" s="1">
+        <f t="shared" si="7"/>
+        <v>137.82639999999998</v>
+      </c>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
@@ -7885,11 +7888,11 @@
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5">
-        <f t="shared" ref="W9:W70" si="7">V9</f>
-        <v>0</v>
-      </c>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
+        <f t="shared" ref="W9:W70" si="8">V9</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
       <c r="Z9" s="1">
         <f t="shared" si="5"/>
         <v>35.666666666666664</v>
@@ -7935,7 +7938,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="1"/>
+      <c r="AN9" s="1">
+        <f t="shared" si="7"/>
+        <v>0.96</v>
+      </c>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
@@ -8002,14 +8008,14 @@
       </c>
       <c r="V10" s="5"/>
       <c r="W10" s="5">
-        <f t="shared" ref="W10:W11" si="8">X10</f>
+        <f t="shared" ref="W10:W11" si="9">X10</f>
         <v>150</v>
       </c>
-      <c r="X10" s="16">
+      <c r="X10" s="1">
         <f>VLOOKUP(A10,[1]Sheet!$A:$X,23,0)</f>
         <v>150</v>
       </c>
-      <c r="Y10" s="16" t="str">
+      <c r="Y10" s="1" t="str">
         <f>VLOOKUP(A10,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -8056,7 +8062,10 @@
         <f t="shared" si="6"/>
         <v>68</v>
       </c>
-      <c r="AN10" s="1"/>
+      <c r="AN10" s="1">
+        <f t="shared" si="7"/>
+        <v>33.21</v>
+      </c>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
       <c r="AQ10" s="1"/>
@@ -8121,14 +8130,14 @@
       </c>
       <c r="V11" s="5"/>
       <c r="W11" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="X11" s="16">
+      <c r="X11" s="1">
         <f>VLOOKUP(A11,[1]Sheet!$A:$X,23,0)</f>
         <v>100</v>
       </c>
-      <c r="Y11" s="16" t="str">
+      <c r="Y11" s="1" t="str">
         <f>VLOOKUP(A11,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -8177,7 +8186,10 @@
         <f t="shared" si="6"/>
         <v>45</v>
       </c>
-      <c r="AN11" s="1"/>
+      <c r="AN11" s="1">
+        <f t="shared" si="7"/>
+        <v>24.57</v>
+      </c>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
@@ -8230,11 +8242,11 @@
       </c>
       <c r="V12" s="12"/>
       <c r="W12" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
       <c r="Z12" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -8280,7 +8292,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="1"/>
+      <c r="AN12" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
@@ -8344,18 +8359,18 @@
         <v>12.4</v>
       </c>
       <c r="V13" s="5">
-        <f t="shared" ref="V13:V22" si="9">11*U13-T13-S13-R13-Q13-P13-O13-F13</f>
+        <f t="shared" ref="V13:V22" si="10">11*U13-T13-S13-R13-Q13-P13-O13-F13</f>
         <v>35.799999999999983</v>
       </c>
       <c r="W13" s="5">
-        <f t="shared" ref="W13:W14" si="10">X13</f>
+        <f t="shared" ref="W13:W14" si="11">X13</f>
         <v>60</v>
       </c>
-      <c r="X13" s="16">
+      <c r="X13" s="1">
         <f>VLOOKUP(A13,[1]Sheet!$A:$X,23,0)</f>
         <v>60</v>
       </c>
-      <c r="Y13" s="16" t="str">
+      <c r="Y13" s="1" t="str">
         <f>VLOOKUP(A13,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -8402,7 +8417,10 @@
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="AN13" s="1"/>
+      <c r="AN13" s="1">
+        <f t="shared" si="7"/>
+        <v>3.7199999999999998</v>
+      </c>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
@@ -8466,18 +8484,18 @@
         <v>37.6</v>
       </c>
       <c r="V14" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>130.60000000000002</v>
       </c>
       <c r="W14" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
-      <c r="X14" s="16">
+      <c r="X14" s="1">
         <f>VLOOKUP(A14,[1]Sheet!$A:$X,23,0)</f>
         <v>200</v>
       </c>
-      <c r="Y14" s="16" t="str">
+      <c r="Y14" s="1" t="str">
         <f>VLOOKUP(A14,[1]Sheet!$A:$X,24,0)</f>
         <v>Сроки большие, так же по данной позиции спрос т.к. постоянные перебои электроснабжения</v>
       </c>
@@ -8524,7 +8542,10 @@
         <f t="shared" si="6"/>
         <v>34</v>
       </c>
-      <c r="AN14" s="1"/>
+      <c r="AN14" s="1">
+        <f t="shared" si="7"/>
+        <v>6.3920000000000003</v>
+      </c>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
       <c r="AQ14" s="1"/>
@@ -8591,11 +8612,11 @@
       </c>
       <c r="V15" s="5"/>
       <c r="W15" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
       <c r="Z15" s="1">
         <f t="shared" si="5"/>
         <v>25.69622649446805</v>
@@ -8639,7 +8660,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="1"/>
+      <c r="AN15" s="1">
+        <f t="shared" si="7"/>
+        <v>47.542000000000002</v>
+      </c>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
       <c r="AQ15" s="1"/>
@@ -8709,11 +8733,11 @@
         <v>6.1825999999989847</v>
       </c>
       <c r="W16" s="5">
-        <f t="shared" ref="W16:W17" si="11">V16+U16*$W$1</f>
+        <f t="shared" ref="W16:W17" si="12">V16+U16*$W$1</f>
         <v>464.42999999999904</v>
       </c>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
       <c r="Z16" s="1">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -8757,7 +8781,10 @@
         <f t="shared" si="6"/>
         <v>464</v>
       </c>
-      <c r="AN16" s="1"/>
+      <c r="AN16" s="1">
+        <f t="shared" si="7"/>
+        <v>458.24740000000003</v>
+      </c>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
       <c r="AQ16" s="1"/>
@@ -8823,15 +8850,15 @@
         <v>22.7486</v>
       </c>
       <c r="V17" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>80.613799999999969</v>
       </c>
       <c r="W17" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>103.36239999999997</v>
       </c>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
       <c r="Z17" s="1">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -8875,7 +8902,10 @@
         <f t="shared" si="6"/>
         <v>103</v>
       </c>
-      <c r="AN17" s="1"/>
+      <c r="AN17" s="1">
+        <f t="shared" si="7"/>
+        <v>22.7486</v>
+      </c>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1"/>
@@ -8940,11 +8970,11 @@
       </c>
       <c r="V18" s="5"/>
       <c r="W18" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
       <c r="Z18" s="1">
         <f t="shared" si="5"/>
         <v>-576.82203389830499</v>
@@ -8988,7 +9018,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="1"/>
+      <c r="AN18" s="1">
+        <f t="shared" si="7"/>
+        <v>-0.16519999999999999</v>
+      </c>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
       <c r="AQ18" s="1"/>
@@ -9053,11 +9086,11 @@
       </c>
       <c r="V19" s="5"/>
       <c r="W19" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
       <c r="Z19" s="1">
         <f t="shared" si="5"/>
         <v>24.66835994194485</v>
@@ -9103,7 +9136,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="1"/>
+      <c r="AN19" s="1">
+        <f t="shared" si="7"/>
+        <v>2.7559999999999998</v>
+      </c>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
@@ -9167,15 +9203,15 @@
         <v>89.878</v>
       </c>
       <c r="V20" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>145.99737759999999</v>
       </c>
       <c r="W20" s="5">
-        <f t="shared" ref="W20:W21" si="12">V20+U20*$W$1</f>
+        <f t="shared" ref="W20:W21" si="13">V20+U20*$W$1</f>
         <v>235.87537759999998</v>
       </c>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
       <c r="Z20" s="1">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -9219,7 +9255,10 @@
         <f t="shared" si="6"/>
         <v>236</v>
       </c>
-      <c r="AN20" s="1"/>
+      <c r="AN20" s="1">
+        <f t="shared" si="7"/>
+        <v>89.878</v>
+      </c>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
       <c r="AQ20" s="1"/>
@@ -9283,15 +9322,15 @@
         <v>28.196199999999997</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>178.74619999999996</v>
       </c>
       <c r="W21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>206.94239999999996</v>
       </c>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="16"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
       <c r="Z21" s="1">
         <f t="shared" si="5"/>
         <v>11.999999999999998</v>
@@ -9335,7 +9374,10 @@
         <f t="shared" si="6"/>
         <v>207</v>
       </c>
-      <c r="AN21" s="1"/>
+      <c r="AN21" s="1">
+        <f t="shared" si="7"/>
+        <v>28.196199999999997</v>
+      </c>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
       <c r="AQ21" s="1"/>
@@ -9401,18 +9443,18 @@
         <v>54.458799999999997</v>
       </c>
       <c r="V22" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>201.08979999999997</v>
       </c>
       <c r="W22" s="5">
         <f>X22</f>
         <v>350</v>
       </c>
-      <c r="X22" s="16">
+      <c r="X22" s="1">
         <f>VLOOKUP(A22,[1]Sheet!$A:$X,23,0)</f>
         <v>350</v>
       </c>
-      <c r="Y22" s="16" t="str">
+      <c r="Y22" s="1" t="str">
         <f>VLOOKUP(A22,[1]Sheet!$A:$X,24,0)</f>
         <v>Промо, сроки большие.</v>
       </c>
@@ -9459,7 +9501,10 @@
         <f t="shared" si="6"/>
         <v>350</v>
       </c>
-      <c r="AN22" s="1"/>
+      <c r="AN22" s="1">
+        <f t="shared" si="7"/>
+        <v>54.458799999999997</v>
+      </c>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
       <c r="AQ22" s="1"/>
@@ -9524,11 +9569,11 @@
       </c>
       <c r="V23" s="5"/>
       <c r="W23" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
       <c r="Z23" s="1">
         <f t="shared" si="5"/>
         <v>33.560254471502326</v>
@@ -9574,7 +9619,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="1"/>
+      <c r="AN23" s="1">
+        <f t="shared" si="7"/>
+        <v>3.8353999999999999</v>
+      </c>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
@@ -9644,11 +9692,11 @@
         <f>X24</f>
         <v>150</v>
       </c>
-      <c r="X24" s="16">
+      <c r="X24" s="1">
         <f>VLOOKUP(A24,[1]Sheet!$A:$X,23,0)</f>
         <v>150</v>
       </c>
-      <c r="Y24" s="16" t="str">
+      <c r="Y24" s="1" t="str">
         <f>VLOOKUP(A24,[1]Sheet!$A:$X,24,0)</f>
         <v>Промо, сроки большие.</v>
       </c>
@@ -9695,7 +9743,10 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AN24" s="1"/>
+      <c r="AN24" s="1">
+        <f t="shared" si="7"/>
+        <v>20.725000000000001</v>
+      </c>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
       <c r="AQ24" s="1"/>
@@ -9754,11 +9805,11 @@
       </c>
       <c r="V25" s="12"/>
       <c r="W25" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
       <c r="Z25" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -9802,7 +9853,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="1"/>
+      <c r="AN25" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
       <c r="AQ25" s="1"/>
@@ -9855,11 +9909,11 @@
       </c>
       <c r="V26" s="12"/>
       <c r="W26" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
       <c r="Z26" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
@@ -9905,7 +9959,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="1"/>
+      <c r="AN26" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
@@ -9970,11 +10027,11 @@
       </c>
       <c r="V27" s="5"/>
       <c r="W27" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
       <c r="Z27" s="1">
         <f t="shared" si="5"/>
         <v>52.349142771580446</v>
@@ -10020,7 +10077,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN27" s="1"/>
+      <c r="AN27" s="1">
+        <f t="shared" si="7"/>
+        <v>5.3427999999999995</v>
+      </c>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
       <c r="AQ27" s="1"/>
@@ -10087,11 +10147,11 @@
         <v>30</v>
       </c>
       <c r="W28" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
       <c r="Z28" s="1">
         <f t="shared" si="5"/>
         <v>13.003747199258287</v>
@@ -10135,7 +10195,10 @@
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="AN28" s="1"/>
+      <c r="AN28" s="1">
+        <f t="shared" si="7"/>
+        <v>5.1772</v>
+      </c>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
       <c r="AQ28" s="1"/>
@@ -10199,18 +10262,18 @@
         <v>34.136399999999995</v>
       </c>
       <c r="V29" s="5">
-        <f t="shared" ref="V29:V31" si="13">11*U29-T29-S29-R29-Q29-P29-O29-F29</f>
+        <f t="shared" ref="V29:V31" si="14">11*U29-T29-S29-R29-Q29-P29-O29-F29</f>
         <v>90.770399999999952</v>
       </c>
       <c r="W29" s="5">
         <f>X29</f>
         <v>150</v>
       </c>
-      <c r="X29" s="16">
+      <c r="X29" s="1">
         <f>VLOOKUP(A29,[1]Sheet!$A:$X,23,0)</f>
         <v>150</v>
       </c>
-      <c r="Y29" s="16" t="str">
+      <c r="Y29" s="1" t="str">
         <f>VLOOKUP(A29,[1]Sheet!$A:$X,24,0)</f>
         <v>Спрос.</v>
       </c>
@@ -10259,7 +10322,10 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AN29" s="1"/>
+      <c r="AN29" s="1">
+        <f t="shared" si="7"/>
+        <v>34.136399999999995</v>
+      </c>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
       <c r="AQ29" s="1"/>
@@ -10324,11 +10390,11 @@
       </c>
       <c r="V30" s="5"/>
       <c r="W30" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
       <c r="Z30" s="1">
         <f t="shared" si="5"/>
         <v>26.427859494397293</v>
@@ -10374,7 +10440,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN30" s="1"/>
+      <c r="AN30" s="1">
+        <f t="shared" si="7"/>
+        <v>79.461600000000004</v>
+      </c>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
       <c r="AQ30" s="1"/>
@@ -10438,15 +10507,15 @@
         <v>6.6069999999999993</v>
       </c>
       <c r="V31" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>54.366199999999992</v>
       </c>
       <c r="W31" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>54.366199999999992</v>
       </c>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
       <c r="Z31" s="1">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -10490,7 +10559,10 @@
         <f t="shared" si="6"/>
         <v>54</v>
       </c>
-      <c r="AN31" s="1"/>
+      <c r="AN31" s="1">
+        <f t="shared" si="7"/>
+        <v>6.6069999999999993</v>
+      </c>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
@@ -10557,11 +10629,11 @@
       </c>
       <c r="V32" s="5"/>
       <c r="W32" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
       <c r="Z32" s="1">
         <f t="shared" si="5"/>
         <v>16.796487990542378</v>
@@ -10607,7 +10679,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="1"/>
+      <c r="AN32" s="1">
+        <f t="shared" si="7"/>
+        <v>13.872399999999999</v>
+      </c>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
       <c r="AQ32" s="1"/>
@@ -10674,11 +10749,11 @@
         <v>150</v>
       </c>
       <c r="W33" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
       <c r="Z33" s="1">
         <f t="shared" si="5"/>
         <v>9.3232255097347849</v>
@@ -10722,7 +10797,10 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="AN33" s="1"/>
+      <c r="AN33" s="1">
+        <f t="shared" si="7"/>
+        <v>26.092000000000002</v>
+      </c>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
@@ -10785,11 +10863,11 @@
       </c>
       <c r="V34" s="12"/>
       <c r="W34" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
       <c r="Z34" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -10833,7 +10911,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN34" s="1"/>
+      <c r="AN34" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
       <c r="AQ34" s="1"/>
@@ -10902,11 +10983,11 @@
         <v>40</v>
       </c>
       <c r="W35" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
       <c r="Z35" s="1">
         <f t="shared" si="5"/>
         <v>7.7269108910891102</v>
@@ -10950,7 +11031,10 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AN35" s="1"/>
+      <c r="AN35" s="1">
+        <f t="shared" si="7"/>
+        <v>10.1</v>
+      </c>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
@@ -11015,11 +11099,11 @@
       </c>
       <c r="V36" s="5"/>
       <c r="W36" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
       <c r="Z36" s="1">
         <f t="shared" si="5"/>
         <v>24.05982905982906</v>
@@ -11063,7 +11147,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="1"/>
+      <c r="AN36" s="1">
+        <f t="shared" si="7"/>
+        <v>9.36</v>
+      </c>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
       <c r="AQ36" s="1"/>
@@ -11128,11 +11215,11 @@
       </c>
       <c r="V37" s="5"/>
       <c r="W37" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X37" s="16"/>
-      <c r="Y37" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
       <c r="Z37" s="1">
         <f t="shared" si="5"/>
         <v>18.155737704918035</v>
@@ -11178,7 +11265,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN37" s="1"/>
+      <c r="AN37" s="1">
+        <f t="shared" si="7"/>
+        <v>10.98</v>
+      </c>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
@@ -11222,7 +11312,7 @@
         <v>215</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="14">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="15">E38-K38</f>
         <v>-119</v>
       </c>
       <c r="M38" s="1"/>
@@ -11238,24 +11328,24 @@
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1">
-        <f t="shared" ref="U38:U69" si="15">E38/5</f>
+        <f t="shared" ref="U38:U69" si="16">E38/5</f>
         <v>19.2</v>
       </c>
       <c r="V38" s="5">
         <v>60</v>
       </c>
       <c r="W38" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>60</v>
       </c>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="16"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
       <c r="Z38" s="1">
         <f t="shared" si="5"/>
         <v>17.447916666666668</v>
       </c>
       <c r="AA38" s="1">
-        <f t="shared" ref="AA38:AA69" si="16">(F38+O38+P38+Q38+R38+S38+T38)/U38</f>
+        <f t="shared" ref="AA38:AA69" si="17">(F38+O38+P38+Q38+R38+S38+T38)/U38</f>
         <v>14.322916666666668</v>
       </c>
       <c r="AB38" s="1">
@@ -11293,7 +11383,10 @@
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="AN38" s="1"/>
+      <c r="AN38" s="1">
+        <f t="shared" si="7"/>
+        <v>7.68</v>
+      </c>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
       <c r="AQ38" s="1"/>
@@ -11333,7 +11426,7 @@
         <v>12</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M39" s="1"/>
@@ -11351,24 +11444,24 @@
       </c>
       <c r="T39" s="1"/>
       <c r="U39" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="V39" s="5">
         <v>30</v>
       </c>
       <c r="W39" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="X39" s="16"/>
-      <c r="Y39" s="16"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
       <c r="Z39" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA39" s="1" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB39" s="1">
@@ -11406,7 +11499,10 @@
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="AN39" s="1"/>
+      <c r="AN39" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1"/>
@@ -11450,7 +11546,7 @@
         <v>45.7</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.3900000000000006</v>
       </c>
       <c r="M40" s="1"/>
@@ -11466,22 +11562,22 @@
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>10.418000000000001</v>
       </c>
       <c r="V40" s="5">
-        <f t="shared" ref="V40:V45" si="17">11*U40-T40-S40-R40-Q40-P40-O40-F40</f>
+        <f t="shared" ref="V40:V45" si="18">11*U40-T40-S40-R40-Q40-P40-O40-F40</f>
         <v>37.222000000000008</v>
       </c>
       <c r="W40" s="5">
         <f>X40</f>
         <v>100</v>
       </c>
-      <c r="X40" s="16">
+      <c r="X40" s="1">
         <f>VLOOKUP(A40,[1]Sheet!$A:$X,23,0)</f>
         <v>100</v>
       </c>
-      <c r="Y40" s="16" t="str">
+      <c r="Y40" s="1" t="str">
         <f>VLOOKUP(A40,[1]Sheet!$A:$X,24,0)</f>
         <v>Промо.</v>
       </c>
@@ -11490,7 +11586,7 @@
         <v>17.025916682664619</v>
       </c>
       <c r="AA40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7.4271453253983486</v>
       </c>
       <c r="AB40" s="1">
@@ -11528,7 +11624,10 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AN40" s="1"/>
+      <c r="AN40" s="1">
+        <f t="shared" si="7"/>
+        <v>10.418000000000001</v>
+      </c>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
       <c r="AQ40" s="1"/>
@@ -11572,7 +11671,7 @@
         <v>545</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="M41" s="1"/>
@@ -11590,22 +11689,22 @@
         <v>305.62880000000013</v>
       </c>
       <c r="U41" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>113.8</v>
       </c>
       <c r="V41" s="5"/>
       <c r="W41" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X41" s="16"/>
-      <c r="Y41" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
       <c r="Z41" s="1">
         <f t="shared" si="5"/>
         <v>13.539543057996489</v>
       </c>
       <c r="AA41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>13.539543057996489</v>
       </c>
       <c r="AB41" s="1">
@@ -11645,7 +11744,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN41" s="1"/>
+      <c r="AN41" s="1">
+        <f t="shared" si="7"/>
+        <v>11.38</v>
+      </c>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
       <c r="AQ41" s="1"/>
@@ -11689,7 +11791,7 @@
         <v>57</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-29</v>
       </c>
       <c r="M42" s="1"/>
@@ -11705,7 +11807,7 @@
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.6</v>
       </c>
       <c r="V42" s="5">
@@ -11714,11 +11816,11 @@
       <c r="W42" s="5">
         <v>150</v>
       </c>
-      <c r="X42" s="16">
+      <c r="X42" s="1">
         <f>VLOOKUP(A42,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y42" s="16" t="str">
+      <c r="Y42" s="1" t="str">
         <f>VLOOKUP(A42,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -11727,7 +11829,7 @@
         <v>35.357142857142861</v>
       </c>
       <c r="AA42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8.5714285714285712</v>
       </c>
       <c r="AB42" s="1">
@@ -11765,7 +11867,10 @@
         <f t="shared" si="6"/>
         <v>53</v>
       </c>
-      <c r="AN42" s="1"/>
+      <c r="AN42" s="1">
+        <f t="shared" si="7"/>
+        <v>1.9599999999999997</v>
+      </c>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
       <c r="AQ42" s="1"/>
@@ -11809,7 +11914,7 @@
         <v>14</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-6.0090000000000003</v>
       </c>
       <c r="M43" s="1"/>
@@ -11825,22 +11930,22 @@
       <c r="S43" s="1"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.5981999999999998</v>
       </c>
       <c r="V43" s="5"/>
       <c r="W43" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X43" s="16"/>
-      <c r="Y43" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
       <c r="Z43" s="1">
         <f t="shared" si="5"/>
         <v>91.93968214241022</v>
       </c>
       <c r="AA43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>91.93968214241022</v>
       </c>
       <c r="AB43" s="1">
@@ -11878,7 +11983,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN43" s="1"/>
+      <c r="AN43" s="1">
+        <f t="shared" si="7"/>
+        <v>1.5981999999999998</v>
+      </c>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
@@ -11922,7 +12030,7 @@
         <v>138</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="M44" s="1"/>
@@ -11940,25 +12048,25 @@
         <v>100</v>
       </c>
       <c r="U44" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28.2</v>
       </c>
       <c r="V44" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>46.199999999999989</v>
       </c>
       <c r="W44" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>46.199999999999989</v>
       </c>
-      <c r="X44" s="16"/>
-      <c r="Y44" s="16"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
       <c r="Z44" s="1">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="AA44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.3617021276595747</v>
       </c>
       <c r="AB44" s="1">
@@ -11996,7 +12104,10 @@
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="AN44" s="1"/>
+      <c r="AN44" s="1">
+        <f t="shared" si="7"/>
+        <v>11.280000000000001</v>
+      </c>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
       <c r="AQ44" s="1"/>
@@ -12040,7 +12151,7 @@
         <v>163</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="M45" s="1"/>
@@ -12058,25 +12169,25 @@
         <v>94.883200000000016</v>
       </c>
       <c r="U45" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>33.4</v>
       </c>
       <c r="V45" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>116.19999999999996</v>
       </c>
       <c r="W45" s="5">
         <f>V45+U45*$W$1</f>
         <v>149.59999999999997</v>
       </c>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
       <c r="Z45" s="1">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="AA45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7.5209580838323369</v>
       </c>
       <c r="AB45" s="1">
@@ -12114,7 +12225,10 @@
         <f t="shared" si="6"/>
         <v>60</v>
       </c>
-      <c r="AN45" s="1"/>
+      <c r="AN45" s="1">
+        <f t="shared" si="7"/>
+        <v>13.36</v>
+      </c>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
@@ -12154,7 +12268,7 @@
         <v>6.4</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-6.4</v>
       </c>
       <c r="M46" s="10"/>
@@ -12170,22 +12284,22 @@
       <c r="S46" s="10"/>
       <c r="T46" s="10"/>
       <c r="U46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="1"/>
+      <c r="Y46" s="1"/>
       <c r="Z46" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA46" s="10" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB46" s="10">
@@ -12223,7 +12337,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN46" s="1"/>
+      <c r="AN46" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
       <c r="AQ46" s="1"/>
@@ -12267,7 +12384,7 @@
         <v>9.4</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-6.5180000000000007</v>
       </c>
       <c r="M47" s="1"/>
@@ -12283,19 +12400,19 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.57640000000000002</v>
       </c>
       <c r="V47" s="5"/>
       <c r="W47" s="5">
-        <f t="shared" ref="W47:W48" si="18">X47</f>
+        <f t="shared" ref="W47:W48" si="19">X47</f>
         <v>100</v>
       </c>
-      <c r="X47" s="16">
+      <c r="X47" s="1">
         <f>VLOOKUP(A47,[1]Sheet!$A:$X,23,0)</f>
         <v>100</v>
       </c>
-      <c r="Y47" s="16" t="str">
+      <c r="Y47" s="1" t="str">
         <f>VLOOKUP(A47,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -12304,7 +12421,7 @@
         <v>329.68598195697433</v>
       </c>
       <c r="AA47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>156.19535045107565</v>
       </c>
       <c r="AB47" s="1">
@@ -12342,7 +12459,10 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AN47" s="1"/>
+      <c r="AN47" s="1">
+        <f t="shared" si="7"/>
+        <v>0.57640000000000002</v>
+      </c>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
       <c r="AQ47" s="1"/>
@@ -12386,7 +12506,7 @@
         <v>210</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-51</v>
       </c>
       <c r="M48" s="1"/>
@@ -12404,21 +12524,21 @@
       </c>
       <c r="T48" s="1"/>
       <c r="U48" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>31.8</v>
       </c>
       <c r="V48" s="5">
         <v>180</v>
       </c>
       <c r="W48" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>250</v>
       </c>
-      <c r="X48" s="16">
+      <c r="X48" s="1">
         <f>VLOOKUP(A48,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y48" s="16" t="str">
+      <c r="Y48" s="1" t="str">
         <f>VLOOKUP(A48,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -12427,7 +12547,7 @@
         <v>14.213836477987421</v>
       </c>
       <c r="AA48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6.3522012578616351</v>
       </c>
       <c r="AB48" s="1">
@@ -12465,7 +12585,10 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="AN48" s="1"/>
+      <c r="AN48" s="1">
+        <f t="shared" si="7"/>
+        <v>11.129999999999999</v>
+      </c>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
       <c r="AQ48" s="1"/>
@@ -12507,7 +12630,7 @@
         <v>205</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-35</v>
       </c>
       <c r="M49" s="1"/>
@@ -12525,24 +12648,24 @@
         <v>100</v>
       </c>
       <c r="U49" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>34</v>
       </c>
       <c r="V49" s="5">
         <v>50</v>
       </c>
       <c r="W49" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
+      <c r="X49" s="1"/>
+      <c r="Y49" s="1"/>
       <c r="Z49" s="1">
         <f t="shared" si="5"/>
         <v>13.235294117647058</v>
       </c>
       <c r="AA49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.764705882352942</v>
       </c>
       <c r="AB49" s="1">
@@ -12580,7 +12703,10 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="AN49" s="1"/>
+      <c r="AN49" s="1">
+        <f t="shared" si="7"/>
+        <v>13.600000000000001</v>
+      </c>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
       <c r="AQ49" s="1"/>
@@ -12624,7 +12750,7 @@
         <v>61.25</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.3199999999999932</v>
       </c>
       <c r="M50" s="1"/>
@@ -12640,25 +12766,25 @@
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13.913999999999998</v>
       </c>
       <c r="V50" s="5">
-        <f t="shared" ref="V50:V60" si="19">11*U50-T50-S50-R50-Q50-P50-O50-F50</f>
+        <f t="shared" ref="V50:V60" si="20">11*U50-T50-S50-R50-Q50-P50-O50-F50</f>
         <v>48.958999999999975</v>
       </c>
       <c r="W50" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>48.958999999999975</v>
       </c>
-      <c r="X50" s="16"/>
-      <c r="Y50" s="16"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
       <c r="Z50" s="1">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="AA50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7.4813137846773046</v>
       </c>
       <c r="AB50" s="1">
@@ -12696,7 +12822,10 @@
         <f t="shared" si="6"/>
         <v>49</v>
       </c>
-      <c r="AN50" s="1"/>
+      <c r="AN50" s="1">
+        <f t="shared" si="7"/>
+        <v>13.913999999999998</v>
+      </c>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
       <c r="AQ50" s="1"/>
@@ -12740,7 +12869,7 @@
         <v>128.25</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.181999999999988</v>
       </c>
       <c r="M51" s="1"/>
@@ -12758,25 +12887,25 @@
         <v>65.323268800000051</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>28.886399999999998</v>
       </c>
       <c r="V51" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>44.487199999999945</v>
       </c>
       <c r="W51" s="5">
         <f>V51+U51*$W$1</f>
         <v>73.373599999999939</v>
       </c>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
       <c r="Z51" s="1">
         <f t="shared" si="5"/>
         <v>11.999999999999998</v>
       </c>
       <c r="AA51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.4599257782208923</v>
       </c>
       <c r="AB51" s="1">
@@ -12816,7 +12945,10 @@
         <f t="shared" si="6"/>
         <v>73</v>
       </c>
-      <c r="AN51" s="1"/>
+      <c r="AN51" s="1">
+        <f t="shared" si="7"/>
+        <v>28.886399999999998</v>
+      </c>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
       <c r="AQ51" s="1"/>
@@ -12854,7 +12986,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M52" s="1"/>
@@ -12874,24 +13006,24 @@
       </c>
       <c r="T52" s="1"/>
       <c r="U52" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="V52" s="5">
         <v>40</v>
       </c>
       <c r="W52" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="X52" s="16"/>
-      <c r="Y52" s="16"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
       <c r="Z52" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA52" s="1" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB52" s="1">
@@ -12929,7 +13061,10 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AN52" s="1"/>
+      <c r="AN52" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
       <c r="AQ52" s="1"/>
@@ -12973,7 +13108,7 @@
         <v>108</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M53" s="1"/>
@@ -12989,25 +13124,25 @@
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
       <c r="U53" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>21.6</v>
       </c>
       <c r="V53" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>24.800000000000068</v>
       </c>
       <c r="W53" s="5">
         <f>V53+U53*$W$1</f>
         <v>46.40000000000007</v>
       </c>
-      <c r="X53" s="16"/>
-      <c r="Y53" s="16"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
       <c r="Z53" s="1">
         <f t="shared" si="5"/>
         <v>12.000000000000002</v>
       </c>
       <c r="AA53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.8518518518518494</v>
       </c>
       <c r="AB53" s="1">
@@ -13045,7 +13180,10 @@
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
-      <c r="AN53" s="1"/>
+      <c r="AN53" s="1">
+        <f t="shared" si="7"/>
+        <v>9.7200000000000006</v>
+      </c>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
       <c r="AQ53" s="1"/>
@@ -13089,7 +13227,7 @@
         <v>133</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-12</v>
       </c>
       <c r="M54" s="1"/>
@@ -13105,22 +13243,22 @@
       <c r="S54" s="1"/>
       <c r="T54" s="1"/>
       <c r="U54" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>24.2</v>
       </c>
       <c r="V54" s="5"/>
       <c r="W54" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X54" s="16"/>
-      <c r="Y54" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
       <c r="Z54" s="1">
         <f t="shared" si="5"/>
         <v>16.735537190082646</v>
       </c>
       <c r="AA54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>16.735537190082646</v>
       </c>
       <c r="AB54" s="1">
@@ -13160,7 +13298,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN54" s="1"/>
+      <c r="AN54" s="1">
+        <f t="shared" si="7"/>
+        <v>10.89</v>
+      </c>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
       <c r="AQ54" s="1"/>
@@ -13202,7 +13343,7 @@
         <v>5</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-2</v>
       </c>
       <c r="M55" s="1"/>
@@ -13220,24 +13361,24 @@
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
       <c r="U55" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="V55" s="5">
         <v>50</v>
       </c>
       <c r="W55" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="X55" s="16"/>
-      <c r="Y55" s="16"/>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
       <c r="Z55" s="1">
         <f t="shared" si="5"/>
         <v>160</v>
       </c>
       <c r="AA55" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>76.666666666666671</v>
       </c>
       <c r="AB55" s="1">
@@ -13275,7 +13416,10 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="AN55" s="1"/>
+      <c r="AN55" s="1">
+        <f t="shared" si="7"/>
+        <v>0.24</v>
+      </c>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
       <c r="AQ55" s="1"/>
@@ -13319,7 +13463,7 @@
         <v>104</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-1</v>
       </c>
       <c r="M56" s="1"/>
@@ -13335,25 +13479,25 @@
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
       <c r="U56" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>20.6</v>
       </c>
       <c r="V56" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>50.600000000000023</v>
       </c>
       <c r="W56" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50.600000000000023</v>
       </c>
-      <c r="X56" s="16"/>
-      <c r="Y56" s="16"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
       <c r="Z56" s="1">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="AA56" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>8.5436893203883493</v>
       </c>
       <c r="AB56" s="1">
@@ -13391,7 +13535,10 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="AN56" s="1"/>
+      <c r="AN56" s="1">
+        <f t="shared" si="7"/>
+        <v>8.24</v>
+      </c>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
       <c r="AQ56" s="1"/>
@@ -13435,7 +13582,7 @@
         <v>53</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4.7139999999999986</v>
       </c>
       <c r="M57" s="1"/>
@@ -13451,22 +13598,22 @@
       <c r="S57" s="1"/>
       <c r="T57" s="1"/>
       <c r="U57" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>11.5428</v>
       </c>
       <c r="V57" s="5"/>
       <c r="W57" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
       <c r="Z57" s="1">
         <f t="shared" si="5"/>
         <v>23.30699656928995</v>
       </c>
       <c r="AA57" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>23.30699656928995</v>
       </c>
       <c r="AB57" s="1">
@@ -13506,7 +13653,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN57" s="1"/>
+      <c r="AN57" s="1">
+        <f t="shared" si="7"/>
+        <v>11.5428</v>
+      </c>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
       <c r="AQ57" s="1"/>
@@ -13552,7 +13702,7 @@
         <v>313</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>239</v>
       </c>
       <c r="M58" s="1"/>
@@ -13570,22 +13720,22 @@
         <v>300</v>
       </c>
       <c r="U58" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>110.4</v>
       </c>
       <c r="V58" s="5"/>
       <c r="W58" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
       <c r="Z58" s="1">
         <f t="shared" si="5"/>
         <v>15.126811594202898</v>
       </c>
       <c r="AA58" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>15.126811594202898</v>
       </c>
       <c r="AB58" s="1">
@@ -13625,7 +13775,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN58" s="1"/>
+      <c r="AN58" s="1">
+        <f t="shared" si="7"/>
+        <v>11.040000000000001</v>
+      </c>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
       <c r="AQ58" s="1"/>
@@ -13669,7 +13822,7 @@
         <v>81.150000000000006</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20.530999999999992</v>
       </c>
       <c r="M59" s="1"/>
@@ -13687,22 +13840,22 @@
         <v>80</v>
       </c>
       <c r="U59" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>20.336199999999998</v>
       </c>
       <c r="V59" s="5"/>
       <c r="W59" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X59" s="16"/>
-      <c r="Y59" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
       <c r="Z59" s="1">
         <f t="shared" si="5"/>
         <v>14.375104493464857</v>
       </c>
       <c r="AA59" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14.375104493464857</v>
       </c>
       <c r="AB59" s="1">
@@ -13742,7 +13895,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN59" s="1"/>
+      <c r="AN59" s="1">
+        <f t="shared" si="7"/>
+        <v>20.336199999999998</v>
+      </c>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
       <c r="AQ59" s="1"/>
@@ -13786,7 +13942,7 @@
         <v>39.65</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.0200000000000031</v>
       </c>
       <c r="M60" s="1"/>
@@ -13802,25 +13958,25 @@
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
       <c r="U60" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.1340000000000003</v>
       </c>
       <c r="V60" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>27.819000000000003</v>
       </c>
       <c r="W60" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>27.819000000000003</v>
       </c>
-      <c r="X60" s="16"/>
-      <c r="Y60" s="16"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
       <c r="Z60" s="1">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="AA60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>7.5799114826653549</v>
       </c>
       <c r="AB60" s="1">
@@ -13858,7 +14014,10 @@
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="AN60" s="1"/>
+      <c r="AN60" s="1">
+        <f t="shared" si="7"/>
+        <v>8.1340000000000003</v>
+      </c>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
       <c r="AQ60" s="1"/>
@@ -13902,7 +14061,7 @@
         <v>339</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="M61" s="1"/>
@@ -13920,22 +14079,22 @@
         <v>200</v>
       </c>
       <c r="U61" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>69.2</v>
       </c>
       <c r="V61" s="5"/>
       <c r="W61" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X61" s="16"/>
-      <c r="Y61" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
       <c r="Z61" s="1">
         <f t="shared" si="5"/>
         <v>18.280346820809246</v>
       </c>
       <c r="AA61" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>18.280346820809246</v>
       </c>
       <c r="AB61" s="1">
@@ -13975,7 +14134,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN61" s="1"/>
+      <c r="AN61" s="1">
+        <f t="shared" si="7"/>
+        <v>6.9200000000000008</v>
+      </c>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
       <c r="AQ61" s="1"/>
@@ -14019,7 +14181,7 @@
         <v>30</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M62" s="1"/>
@@ -14035,22 +14197,22 @@
       <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="V62" s="5"/>
       <c r="W62" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X62" s="16"/>
-      <c r="Y62" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
       <c r="Z62" s="1">
         <f t="shared" si="5"/>
         <v>11.533333333333331</v>
       </c>
       <c r="AA62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.533333333333331</v>
       </c>
       <c r="AB62" s="1">
@@ -14088,7 +14250,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN62" s="1"/>
+      <c r="AN62" s="1">
+        <f t="shared" si="7"/>
+        <v>2.4000000000000004</v>
+      </c>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
       <c r="AQ62" s="1"/>
@@ -14132,7 +14297,7 @@
         <v>46.1</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.2920000000000016</v>
       </c>
       <c r="M63" s="1"/>
@@ -14148,19 +14313,19 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.4784000000000006</v>
       </c>
       <c r="V63" s="5"/>
       <c r="W63" s="5">
-        <f t="shared" ref="W63:W64" si="20">X63</f>
+        <f t="shared" ref="W63:W64" si="21">X63</f>
         <v>100</v>
       </c>
-      <c r="X63" s="16">
+      <c r="X63" s="1">
         <f>VLOOKUP(A63,[1]Sheet!$A:$X,23,0)</f>
         <v>100</v>
       </c>
-      <c r="Y63" s="16" t="str">
+      <c r="Y63" s="1" t="str">
         <f>VLOOKUP(A63,[1]Sheet!$A:$X,24,0)</f>
         <v>Промо.</v>
       </c>
@@ -14169,7 +14334,7 @@
         <v>31.737803848750843</v>
       </c>
       <c r="AA63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>21.1875</v>
       </c>
       <c r="AB63" s="1">
@@ -14207,7 +14372,10 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AN63" s="1"/>
+      <c r="AN63" s="1">
+        <f t="shared" si="7"/>
+        <v>9.4784000000000006</v>
+      </c>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
       <c r="AQ63" s="1"/>
@@ -14249,7 +14417,7 @@
         <v>174.6</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-40.936000000000007</v>
       </c>
       <c r="M64" s="1"/>
@@ -14265,19 +14433,19 @@
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>26.732799999999997</v>
       </c>
       <c r="V64" s="5"/>
       <c r="W64" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>50</v>
       </c>
-      <c r="X64" s="16">
+      <c r="X64" s="1">
         <f>VLOOKUP(A64,[1]Sheet!$A:$X,23,0)</f>
         <v>50</v>
       </c>
-      <c r="Y64" s="16" t="str">
+      <c r="Y64" s="1" t="str">
         <f>VLOOKUP(A64,[1]Sheet!$A:$X,24,0)</f>
         <v>Промо.</v>
       </c>
@@ -14286,7 +14454,7 @@
         <v>24.3272608929854</v>
       </c>
       <c r="AA64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.45689938951401</v>
       </c>
       <c r="AB64" s="1">
@@ -14326,7 +14494,10 @@
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="AN64" s="1"/>
+      <c r="AN64" s="1">
+        <f t="shared" si="7"/>
+        <v>26.732799999999997</v>
+      </c>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
       <c r="AQ64" s="1"/>
@@ -14370,7 +14541,7 @@
         <v>653</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-557</v>
       </c>
       <c r="M65" s="1"/>
@@ -14386,22 +14557,22 @@
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
       <c r="U65" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>19.2</v>
       </c>
       <c r="V65" s="5"/>
       <c r="W65" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X65" s="16"/>
-      <c r="Y65" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
       <c r="Z65" s="1">
         <f t="shared" si="5"/>
         <v>33.4375</v>
       </c>
       <c r="AA65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>33.4375</v>
       </c>
       <c r="AB65" s="1">
@@ -14441,7 +14612,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN65" s="1"/>
+      <c r="AN65" s="1">
+        <f t="shared" si="7"/>
+        <v>7.68</v>
+      </c>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
       <c r="AQ65" s="1"/>
@@ -14485,7 +14659,7 @@
         <v>333</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-38</v>
       </c>
       <c r="M66" s="1"/>
@@ -14503,22 +14677,22 @@
         <v>254.6112</v>
       </c>
       <c r="U66" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>59</v>
       </c>
       <c r="V66" s="5"/>
       <c r="W66" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X66" s="16"/>
-      <c r="Y66" s="16"/>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
       <c r="Z66" s="1">
         <f t="shared" si="5"/>
         <v>16.322033898305083</v>
       </c>
       <c r="AA66" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>16.322033898305083</v>
       </c>
       <c r="AB66" s="1">
@@ -14556,7 +14730,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AN66" s="1"/>
+      <c r="AN66" s="1">
+        <f t="shared" si="7"/>
+        <v>23.6</v>
+      </c>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
       <c r="AQ66" s="1"/>
@@ -14600,7 +14777,7 @@
         <v>17.2</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-6.3649999999999984</v>
       </c>
       <c r="M67" s="1"/>
@@ -14616,19 +14793,19 @@
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
       <c r="U67" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.1670000000000003</v>
       </c>
       <c r="V67" s="5"/>
       <c r="W67" s="5">
-        <f t="shared" ref="W67:W68" si="21">X67</f>
+        <f t="shared" ref="W67:W68" si="22">X67</f>
         <v>70</v>
       </c>
-      <c r="X67" s="16">
+      <c r="X67" s="1">
         <f>VLOOKUP(A67,[1]Sheet!$A:$X,23,0)</f>
         <v>70</v>
       </c>
-      <c r="Y67" s="16" t="str">
+      <c r="Y67" s="1" t="str">
         <f>VLOOKUP(A67,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -14637,7 +14814,7 @@
         <v>86.791139824642343</v>
       </c>
       <c r="AA67" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>54.488417166589748</v>
       </c>
       <c r="AB67" s="1">
@@ -14675,7 +14852,10 @@
         <f t="shared" si="6"/>
         <v>70</v>
       </c>
-      <c r="AN67" s="1"/>
+      <c r="AN67" s="1">
+        <f t="shared" si="7"/>
+        <v>2.1670000000000003</v>
+      </c>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
       <c r="AQ67" s="1"/>
@@ -14715,7 +14895,7 @@
         <v>4.8</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-4.8</v>
       </c>
       <c r="M68" s="1"/>
@@ -14735,21 +14915,21 @@
       </c>
       <c r="T68" s="1"/>
       <c r="U68" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="V68" s="5">
         <v>50</v>
       </c>
       <c r="W68" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>100</v>
       </c>
-      <c r="X68" s="16">
+      <c r="X68" s="1">
         <f>VLOOKUP(A68,[1]Sheet!$A:$X,23,0)</f>
         <v>100</v>
       </c>
-      <c r="Y68" s="16" t="str">
+      <c r="Y68" s="1" t="str">
         <f>VLOOKUP(A68,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
@@ -14758,7 +14938,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AA68" s="1" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB68" s="1">
@@ -14796,7 +14976,10 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AN68" s="1"/>
+      <c r="AN68" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
       <c r="AQ68" s="1"/>
@@ -14838,7 +15021,7 @@
         <v>34.299999999999997</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-43.927999999999997</v>
       </c>
       <c r="M69" s="1"/>
@@ -14856,24 +15039,24 @@
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1.9256</v>
       </c>
       <c r="V69" s="5">
         <v>100</v>
       </c>
       <c r="W69" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="X69" s="16"/>
-      <c r="Y69" s="16"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
       <c r="Z69" s="1">
         <f t="shared" si="5"/>
         <v>-92.127129206481101</v>
       </c>
       <c r="AA69" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-40.195263813876196</v>
       </c>
       <c r="AB69" s="1">
@@ -14911,7 +15094,10 @@
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AN69" s="1"/>
+      <c r="AN69" s="1">
+        <f t="shared" si="7"/>
+        <v>-1.9256</v>
+      </c>
       <c r="AO69" s="1"/>
       <c r="AP69" s="1"/>
       <c r="AQ69" s="1"/>
@@ -14955,7 +15141,7 @@
         <v>33.200000000000003</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="22">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="23">E70-K70</f>
         <v>-23.269000000000005</v>
       </c>
       <c r="M70" s="1"/>
@@ -14975,24 +15161,24 @@
       </c>
       <c r="T70" s="1"/>
       <c r="U70" s="1">
-        <f t="shared" ref="U70:U101" si="23">E70/5</f>
+        <f t="shared" ref="U70:U101" si="24">E70/5</f>
         <v>1.9861999999999997</v>
       </c>
       <c r="V70" s="5">
         <v>40</v>
       </c>
       <c r="W70" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="X70" s="16"/>
-      <c r="Y70" s="16"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
       <c r="Z70" s="1">
         <f t="shared" si="5"/>
         <v>38.936965058906459</v>
       </c>
       <c r="AA70" s="1">
-        <f t="shared" ref="AA70:AA101" si="24">(F70+O70+P70+Q70+R70+S70+T70)/U70</f>
+        <f t="shared" ref="AA70:AA101" si="25">(F70+O70+P70+Q70+R70+S70+T70)/U70</f>
         <v>18.798006243077232</v>
       </c>
       <c r="AB70" s="1">
@@ -15030,7 +15216,10 @@
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AN70" s="1"/>
+      <c r="AN70" s="1">
+        <f t="shared" si="7"/>
+        <v>1.9861999999999997</v>
+      </c>
       <c r="AO70" s="1"/>
       <c r="AP70" s="1"/>
       <c r="AQ70" s="1"/>
@@ -15072,7 +15261,7 @@
         <v>13</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M71" s="1"/>
@@ -15088,22 +15277,22 @@
       <c r="S71" s="1"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.6</v>
       </c>
       <c r="V71" s="5"/>
       <c r="W71" s="5">
-        <f t="shared" ref="W71:W134" si="25">V71</f>
-        <v>0</v>
-      </c>
-      <c r="X71" s="16"/>
-      <c r="Y71" s="16"/>
+        <f t="shared" ref="W71:W134" si="26">V71</f>
+        <v>0</v>
+      </c>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
       <c r="Z71" s="1">
-        <f t="shared" ref="Z71:Z134" si="26">(F71+O71+P71+Q71+R71+S71+T71+W71)/U71</f>
+        <f t="shared" ref="Z71:Z134" si="27">(F71+O71+P71+Q71+R71+S71+T71+W71)/U71</f>
         <v>19.076923076923073</v>
       </c>
       <c r="AA71" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>19.076923076923073</v>
       </c>
       <c r="AB71" s="1">
@@ -15138,10 +15327,13 @@
       </c>
       <c r="AL71" s="1"/>
       <c r="AM71" s="1">
-        <f t="shared" ref="AM71:AM134" si="27">ROUND(G71*W71,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AN71" s="1"/>
+        <f t="shared" ref="AM71:AM134" si="28">ROUND(G71*W71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AN71" s="1">
+        <f t="shared" ref="AN71:AN134" si="29">U71*G71</f>
+        <v>1.56</v>
+      </c>
       <c r="AO71" s="1"/>
       <c r="AP71" s="1"/>
       <c r="AQ71" s="1"/>
@@ -15183,7 +15375,7 @@
         <v>375.55</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-92.840000000000032</v>
       </c>
       <c r="M72" s="1"/>
@@ -15201,22 +15393,22 @@
         <v>200</v>
       </c>
       <c r="U72" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>56.541999999999994</v>
       </c>
       <c r="V72" s="5"/>
       <c r="W72" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1">
+        <f t="shared" si="27"/>
+        <v>21.146308938488207</v>
+      </c>
+      <c r="AA72" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X72" s="16"/>
-      <c r="Y72" s="16"/>
-      <c r="Z72" s="1">
-        <f t="shared" si="26"/>
-        <v>21.146308938488207</v>
-      </c>
-      <c r="AA72" s="1">
-        <f t="shared" si="24"/>
         <v>21.146308938488207</v>
       </c>
       <c r="AB72" s="1">
@@ -15253,10 +15445,13 @@
         <v>48</v>
       </c>
       <c r="AM72" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN72" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN72" s="1">
+        <f t="shared" si="29"/>
+        <v>56.541999999999994</v>
+      </c>
       <c r="AO72" s="1"/>
       <c r="AP72" s="1"/>
       <c r="AQ72" s="1"/>
@@ -15288,7 +15483,7 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M73" s="10"/>
@@ -15304,22 +15499,22 @@
       <c r="S73" s="10"/>
       <c r="T73" s="10"/>
       <c r="U73" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V73" s="12"/>
       <c r="W73" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA73" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X73" s="16"/>
-      <c r="Y73" s="16"/>
-      <c r="Z73" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA73" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB73" s="10">
@@ -15356,10 +15551,13 @@
         <v>50</v>
       </c>
       <c r="AM73" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN73" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN73" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO73" s="1"/>
       <c r="AP73" s="1"/>
       <c r="AQ73" s="1"/>
@@ -15403,7 +15601,7 @@
         <v>39</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8</v>
       </c>
       <c r="M74" s="1"/>
@@ -15419,22 +15617,22 @@
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
       <c r="U74" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.4</v>
       </c>
       <c r="V74" s="5"/>
       <c r="W74" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X74" s="1"/>
+      <c r="Y74" s="1"/>
+      <c r="Z74" s="1">
+        <f t="shared" si="27"/>
+        <v>25.851063829787233</v>
+      </c>
+      <c r="AA74" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X74" s="16"/>
-      <c r="Y74" s="16"/>
-      <c r="Z74" s="1">
-        <f t="shared" si="26"/>
-        <v>25.851063829787233</v>
-      </c>
-      <c r="AA74" s="1">
-        <f t="shared" si="24"/>
         <v>25.851063829787233</v>
       </c>
       <c r="AB74" s="1">
@@ -15471,10 +15669,13 @@
         <v>79</v>
       </c>
       <c r="AM74" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN74" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN74" s="1">
+        <f t="shared" si="29"/>
+        <v>5.64</v>
+      </c>
       <c r="AO74" s="1"/>
       <c r="AP74" s="1"/>
       <c r="AQ74" s="1"/>
@@ -15518,7 +15719,7 @@
         <v>93</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="M75" s="1"/>
@@ -15534,31 +15735,31 @@
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
       <c r="U75" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="V75" s="5">
-        <f t="shared" ref="V75:V77" si="28">11*U75-T75-S75-R75-Q75-P75-O75-F75</f>
+        <f t="shared" ref="V75:V77" si="30">11*U75-T75-S75-R75-Q75-P75-O75-F75</f>
         <v>77.799999999999983</v>
       </c>
       <c r="W75" s="5">
-        <f t="shared" ref="W75:W77" si="29">X75</f>
+        <f t="shared" ref="W75:W77" si="31">X75</f>
         <v>150</v>
       </c>
-      <c r="X75" s="16">
+      <c r="X75" s="1">
         <f>VLOOKUP(A75,[1]Sheet!$A:$X,23,0)</f>
         <v>150</v>
       </c>
-      <c r="Y75" s="16" t="str">
+      <c r="Y75" s="1" t="str">
         <f>VLOOKUP(A75,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, сроки большие</v>
       </c>
       <c r="Z75" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14.610000000000003</v>
       </c>
       <c r="AA75" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7.1100000000000012</v>
       </c>
       <c r="AB75" s="1">
@@ -15593,10 +15794,13 @@
       </c>
       <c r="AL75" s="1"/>
       <c r="AM75" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>60</v>
       </c>
-      <c r="AN75" s="1"/>
+      <c r="AN75" s="1">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
       <c r="AO75" s="1"/>
       <c r="AP75" s="1"/>
       <c r="AQ75" s="1"/>
@@ -15640,7 +15844,7 @@
         <v>196</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13</v>
       </c>
       <c r="M76" s="1"/>
@@ -15658,30 +15862,30 @@
       </c>
       <c r="T76" s="1"/>
       <c r="U76" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>41.8</v>
       </c>
       <c r="V76" s="5">
         <v>150</v>
       </c>
       <c r="W76" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>200</v>
       </c>
-      <c r="X76" s="16">
+      <c r="X76" s="1">
         <f>VLOOKUP(A76,[1]Sheet!$A:$X,23,0)</f>
         <v>200</v>
       </c>
-      <c r="Y76" s="16" t="str">
+      <c r="Y76" s="1" t="str">
         <f>VLOOKUP(A76,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, сроки большие</v>
       </c>
       <c r="Z76" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.4976076555023923</v>
       </c>
       <c r="AA76" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.7129186602870821</v>
       </c>
       <c r="AB76" s="1">
@@ -15716,10 +15920,13 @@
       </c>
       <c r="AL76" s="1"/>
       <c r="AM76" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>66</v>
       </c>
-      <c r="AN76" s="1"/>
+      <c r="AN76" s="1">
+        <f t="shared" si="29"/>
+        <v>13.794</v>
+      </c>
       <c r="AO76" s="1"/>
       <c r="AP76" s="1"/>
       <c r="AQ76" s="1"/>
@@ -15763,7 +15970,7 @@
         <v>114</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5</v>
       </c>
       <c r="M77" s="1"/>
@@ -15781,31 +15988,31 @@
       </c>
       <c r="T77" s="1"/>
       <c r="U77" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>23.8</v>
       </c>
       <c r="V77" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>110.60000000000002</v>
       </c>
       <c r="W77" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>200</v>
       </c>
-      <c r="X77" s="16">
+      <c r="X77" s="1">
         <f>VLOOKUP(A77,[1]Sheet!$A:$X,23,0)</f>
         <v>200</v>
       </c>
-      <c r="Y77" s="16" t="str">
+      <c r="Y77" s="1" t="str">
         <f>VLOOKUP(A77,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, сроки большие</v>
       </c>
       <c r="Z77" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14.756302521008402</v>
       </c>
       <c r="AA77" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.3529411764705879</v>
       </c>
       <c r="AB77" s="1">
@@ -15840,10 +16047,13 @@
       </c>
       <c r="AL77" s="1"/>
       <c r="AM77" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>70</v>
       </c>
-      <c r="AN77" s="1"/>
+      <c r="AN77" s="1">
+        <f t="shared" si="29"/>
+        <v>8.33</v>
+      </c>
       <c r="AO77" s="1"/>
       <c r="AP77" s="1"/>
       <c r="AQ77" s="1"/>
@@ -15887,7 +16097,7 @@
         <v>91</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M78" s="1"/>
@@ -15903,22 +16113,22 @@
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
       <c r="U78" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>18.2</v>
       </c>
       <c r="V78" s="5"/>
       <c r="W78" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
+      <c r="Z78" s="1">
+        <f t="shared" si="27"/>
+        <v>32.142857142857146</v>
+      </c>
+      <c r="AA78" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X78" s="16"/>
-      <c r="Y78" s="16"/>
-      <c r="Z78" s="1">
-        <f t="shared" si="26"/>
-        <v>32.142857142857146</v>
-      </c>
-      <c r="AA78" s="1">
-        <f t="shared" si="24"/>
         <v>32.142857142857146</v>
       </c>
       <c r="AB78" s="1">
@@ -15955,10 +16165,13 @@
         <v>79</v>
       </c>
       <c r="AM78" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN78" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN78" s="1">
+        <f t="shared" si="29"/>
+        <v>6.734</v>
+      </c>
       <c r="AO78" s="1"/>
       <c r="AP78" s="1"/>
       <c r="AQ78" s="1"/>
@@ -15990,7 +16203,7 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M79" s="10"/>
@@ -16006,22 +16219,22 @@
       <c r="S79" s="10"/>
       <c r="T79" s="10"/>
       <c r="U79" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V79" s="12"/>
       <c r="W79" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
+      <c r="Z79" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA79" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X79" s="16"/>
-      <c r="Y79" s="16"/>
-      <c r="Z79" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA79" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB79" s="10">
@@ -16058,10 +16271,13 @@
         <v>50</v>
       </c>
       <c r="AM79" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN79" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN79" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO79" s="1"/>
       <c r="AP79" s="1"/>
       <c r="AQ79" s="1"/>
@@ -16103,7 +16319,7 @@
         <v>74</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-18</v>
       </c>
       <c r="M80" s="1"/>
@@ -16121,22 +16337,22 @@
         <v>125.3984</v>
       </c>
       <c r="U80" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>11.2</v>
       </c>
       <c r="V80" s="5"/>
       <c r="W80" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
+      <c r="Z80" s="1">
+        <f t="shared" si="27"/>
+        <v>31.196428571428573</v>
+      </c>
+      <c r="AA80" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X80" s="16"/>
-      <c r="Y80" s="16"/>
-      <c r="Z80" s="1">
-        <f t="shared" si="26"/>
-        <v>31.196428571428573</v>
-      </c>
-      <c r="AA80" s="1">
-        <f t="shared" si="24"/>
         <v>31.196428571428573</v>
       </c>
       <c r="AB80" s="1">
@@ -16171,10 +16387,13 @@
       </c>
       <c r="AL80" s="1"/>
       <c r="AM80" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN80" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN80" s="1">
+        <f t="shared" si="29"/>
+        <v>3.6959999999999997</v>
+      </c>
       <c r="AO80" s="1"/>
       <c r="AP80" s="1"/>
       <c r="AQ80" s="1"/>
@@ -16218,7 +16437,7 @@
         <v>58</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5</v>
       </c>
       <c r="M81" s="1"/>
@@ -16234,25 +16453,25 @@
       <c r="S81" s="1"/>
       <c r="T81" s="1"/>
       <c r="U81" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>12.6</v>
       </c>
       <c r="V81" s="5">
-        <f t="shared" ref="V81" si="30">11*U81-T81-S81-R81-Q81-P81-O81-F81</f>
+        <f t="shared" ref="V81" si="32">11*U81-T81-S81-R81-Q81-P81-O81-F81</f>
         <v>7.5999999999999943</v>
       </c>
       <c r="W81" s="5">
+        <f t="shared" si="26"/>
+        <v>7.5999999999999943</v>
+      </c>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
+      <c r="Z81" s="1">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="AA81" s="1">
         <f t="shared" si="25"/>
-        <v>7.5999999999999943</v>
-      </c>
-      <c r="X81" s="16"/>
-      <c r="Y81" s="16"/>
-      <c r="Z81" s="1">
-        <f t="shared" si="26"/>
-        <v>11</v>
-      </c>
-      <c r="AA81" s="1">
-        <f t="shared" si="24"/>
         <v>10.396825396825397</v>
       </c>
       <c r="AB81" s="1">
@@ -16287,10 +16506,13 @@
       </c>
       <c r="AL81" s="1"/>
       <c r="AM81" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3</v>
       </c>
-      <c r="AN81" s="1"/>
+      <c r="AN81" s="1">
+        <f t="shared" si="29"/>
+        <v>5.04</v>
+      </c>
       <c r="AO81" s="1"/>
       <c r="AP81" s="1"/>
       <c r="AQ81" s="1"/>
@@ -16330,7 +16552,7 @@
         <v>18</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-18</v>
       </c>
       <c r="M82" s="1"/>
@@ -16350,24 +16572,24 @@
       </c>
       <c r="T82" s="1"/>
       <c r="U82" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V82" s="5">
         <v>20</v>
       </c>
       <c r="W82" s="5">
+        <f t="shared" si="26"/>
+        <v>20</v>
+      </c>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
+      <c r="Z82" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA82" s="1" t="e">
         <f t="shared" si="25"/>
-        <v>20</v>
-      </c>
-      <c r="X82" s="16"/>
-      <c r="Y82" s="16"/>
-      <c r="Z82" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA82" s="1" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB82" s="1">
@@ -16402,10 +16624,13 @@
       </c>
       <c r="AL82" s="1"/>
       <c r="AM82" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7</v>
       </c>
-      <c r="AN82" s="1"/>
+      <c r="AN82" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO82" s="1"/>
       <c r="AP82" s="1"/>
       <c r="AQ82" s="1"/>
@@ -16449,7 +16674,7 @@
         <v>18</v>
       </c>
       <c r="L83" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-5</v>
       </c>
       <c r="M83" s="1"/>
@@ -16465,22 +16690,22 @@
       <c r="S83" s="1"/>
       <c r="T83" s="1"/>
       <c r="U83" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2.6</v>
       </c>
       <c r="V83" s="5"/>
       <c r="W83" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
+      <c r="Z83" s="1">
+        <f t="shared" si="27"/>
+        <v>26.23076923076923</v>
+      </c>
+      <c r="AA83" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X83" s="16"/>
-      <c r="Y83" s="16"/>
-      <c r="Z83" s="1">
-        <f t="shared" si="26"/>
-        <v>26.23076923076923</v>
-      </c>
-      <c r="AA83" s="1">
-        <f t="shared" si="24"/>
         <v>26.23076923076923</v>
       </c>
       <c r="AB83" s="1">
@@ -16515,10 +16740,13 @@
       </c>
       <c r="AL83" s="1"/>
       <c r="AM83" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN83" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN83" s="1">
+        <f t="shared" si="29"/>
+        <v>0.90999999999999992</v>
+      </c>
       <c r="AO83" s="1"/>
       <c r="AP83" s="1"/>
       <c r="AQ83" s="1"/>
@@ -16550,7 +16778,7 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M84" s="10"/>
@@ -16566,22 +16794,22 @@
       <c r="S84" s="10"/>
       <c r="T84" s="10"/>
       <c r="U84" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V84" s="12"/>
       <c r="W84" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
+      <c r="Z84" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA84" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X84" s="16"/>
-      <c r="Y84" s="16"/>
-      <c r="Z84" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA84" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB84" s="10">
@@ -16618,10 +16846,13 @@
         <v>50</v>
       </c>
       <c r="AM84" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN84" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN84" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO84" s="1"/>
       <c r="AP84" s="1"/>
       <c r="AQ84" s="1"/>
@@ -16653,7 +16884,7 @@
       <c r="J85" s="10"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M85" s="10"/>
@@ -16669,22 +16900,22 @@
       <c r="S85" s="10"/>
       <c r="T85" s="10"/>
       <c r="U85" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V85" s="12"/>
       <c r="W85" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
+      <c r="Z85" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA85" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X85" s="16"/>
-      <c r="Y85" s="16"/>
-      <c r="Z85" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA85" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB85" s="10">
@@ -16721,10 +16952,13 @@
         <v>50</v>
       </c>
       <c r="AM85" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN85" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN85" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO85" s="1"/>
       <c r="AP85" s="1"/>
       <c r="AQ85" s="1"/>
@@ -16762,7 +16996,7 @@
       <c r="J86" s="10"/>
       <c r="K86" s="10"/>
       <c r="L86" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M86" s="10"/>
@@ -16778,22 +17012,22 @@
       <c r="S86" s="10"/>
       <c r="T86" s="10"/>
       <c r="U86" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V86" s="12"/>
       <c r="W86" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
+      <c r="Z86" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA86" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X86" s="16"/>
-      <c r="Y86" s="16"/>
-      <c r="Z86" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA86" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB86" s="10">
@@ -16828,10 +17062,13 @@
       </c>
       <c r="AL86" s="10"/>
       <c r="AM86" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN86" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN86" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO86" s="1"/>
       <c r="AP86" s="1"/>
       <c r="AQ86" s="1"/>
@@ -16875,7 +17112,7 @@
         <v>25.8</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-2.8620000000000019</v>
       </c>
       <c r="M87" s="1"/>
@@ -16891,25 +17128,25 @@
       <c r="S87" s="1"/>
       <c r="T87" s="1"/>
       <c r="U87" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>4.5876000000000001</v>
       </c>
       <c r="V87" s="5">
-        <f t="shared" ref="V87" si="31">11*U87-T87-S87-R87-Q87-P87-O87-F87</f>
+        <f t="shared" ref="V87" si="33">11*U87-T87-S87-R87-Q87-P87-O87-F87</f>
         <v>12.474800000000013</v>
       </c>
       <c r="W87" s="5">
+        <f t="shared" si="26"/>
+        <v>12.474800000000013</v>
+      </c>
+      <c r="X87" s="1"/>
+      <c r="Y87" s="1"/>
+      <c r="Z87" s="1">
+        <f t="shared" si="27"/>
+        <v>11</v>
+      </c>
+      <c r="AA87" s="1">
         <f t="shared" si="25"/>
-        <v>12.474800000000013</v>
-      </c>
-      <c r="X87" s="16"/>
-      <c r="Y87" s="16"/>
-      <c r="Z87" s="1">
-        <f t="shared" si="26"/>
-        <v>11</v>
-      </c>
-      <c r="AA87" s="1">
-        <f t="shared" si="24"/>
         <v>8.2807568227395567</v>
       </c>
       <c r="AB87" s="1">
@@ -16944,10 +17181,13 @@
       </c>
       <c r="AL87" s="1"/>
       <c r="AM87" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>12</v>
       </c>
-      <c r="AN87" s="1"/>
+      <c r="AN87" s="1">
+        <f t="shared" si="29"/>
+        <v>4.5876000000000001</v>
+      </c>
       <c r="AO87" s="1"/>
       <c r="AP87" s="1"/>
       <c r="AQ87" s="1"/>
@@ -16991,7 +17231,7 @@
         <v>142.4</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-4.9080000000000155</v>
       </c>
       <c r="M88" s="1"/>
@@ -17009,22 +17249,22 @@
         <v>89.98443759999995</v>
       </c>
       <c r="U88" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>27.498399999999997</v>
       </c>
       <c r="V88" s="5"/>
       <c r="W88" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X88" s="1"/>
+      <c r="Y88" s="1"/>
+      <c r="Z88" s="1">
+        <f t="shared" si="27"/>
+        <v>19.233846041951534</v>
+      </c>
+      <c r="AA88" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X88" s="16"/>
-      <c r="Y88" s="16"/>
-      <c r="Z88" s="1">
-        <f t="shared" si="26"/>
-        <v>19.233846041951534</v>
-      </c>
-      <c r="AA88" s="1">
-        <f t="shared" si="24"/>
         <v>19.233846041951534</v>
       </c>
       <c r="AB88" s="1">
@@ -17059,10 +17299,13 @@
       </c>
       <c r="AL88" s="1"/>
       <c r="AM88" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN88" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN88" s="1">
+        <f t="shared" si="29"/>
+        <v>27.498399999999997</v>
+      </c>
       <c r="AO88" s="1"/>
       <c r="AP88" s="1"/>
       <c r="AQ88" s="1"/>
@@ -17094,7 +17337,7 @@
       <c r="J89" s="10"/>
       <c r="K89" s="10"/>
       <c r="L89" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M89" s="10"/>
@@ -17110,22 +17353,22 @@
       <c r="S89" s="10"/>
       <c r="T89" s="10"/>
       <c r="U89" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V89" s="12"/>
       <c r="W89" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X89" s="1"/>
+      <c r="Y89" s="1"/>
+      <c r="Z89" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA89" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X89" s="16"/>
-      <c r="Y89" s="16"/>
-      <c r="Z89" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA89" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB89" s="10">
@@ -17162,10 +17405,13 @@
         <v>50</v>
       </c>
       <c r="AM89" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN89" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN89" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO89" s="1"/>
       <c r="AP89" s="1"/>
       <c r="AQ89" s="1"/>
@@ -17209,7 +17455,7 @@
         <v>1619.5</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13.188000000000102</v>
       </c>
       <c r="M90" s="1"/>
@@ -17227,25 +17473,25 @@
         <v>198.12029359999991</v>
       </c>
       <c r="U90" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>326.5376</v>
       </c>
       <c r="V90" s="5">
-        <f t="shared" ref="V90:V92" si="32">10*U90-T90-S90-R90-Q90-P90-O90-F90</f>
+        <f t="shared" ref="V90:V92" si="34">10*U90-T90-S90-R90-Q90-P90-O90-F90</f>
         <v>417.58632800000032</v>
       </c>
       <c r="W90" s="5">
-        <f t="shared" ref="W90:W92" si="33">V90+U90*$W$1</f>
+        <f t="shared" ref="W90:W92" si="35">V90+U90*$W$1</f>
         <v>744.12392800000032</v>
       </c>
-      <c r="X90" s="16"/>
-      <c r="Y90" s="16"/>
+      <c r="X90" s="1"/>
+      <c r="Y90" s="1"/>
       <c r="Z90" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.000000000000002</v>
       </c>
       <c r="AA90" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8.7211692374783176</v>
       </c>
       <c r="AB90" s="1">
@@ -17280,10 +17526,13 @@
       </c>
       <c r="AL90" s="1"/>
       <c r="AM90" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>744</v>
       </c>
-      <c r="AN90" s="1"/>
+      <c r="AN90" s="1">
+        <f t="shared" si="29"/>
+        <v>326.5376</v>
+      </c>
       <c r="AO90" s="1"/>
       <c r="AP90" s="1"/>
       <c r="AQ90" s="1"/>
@@ -17327,7 +17576,7 @@
         <v>2074</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>48.436999999999898</v>
       </c>
       <c r="M91" s="1"/>
@@ -17347,25 +17596,25 @@
         <v>1000</v>
       </c>
       <c r="U91" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>424.48739999999998</v>
       </c>
       <c r="V91" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>159.05019999999914</v>
       </c>
       <c r="W91" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>583.53759999999909</v>
       </c>
-      <c r="X91" s="16"/>
-      <c r="Y91" s="16"/>
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
       <c r="Z91" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10.999999999999998</v>
       </c>
       <c r="AA91" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.6253123178685644</v>
       </c>
       <c r="AB91" s="1">
@@ -17400,10 +17649,13 @@
       </c>
       <c r="AL91" s="1"/>
       <c r="AM91" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>584</v>
       </c>
-      <c r="AN91" s="1"/>
+      <c r="AN91" s="1">
+        <f t="shared" si="29"/>
+        <v>424.48739999999998</v>
+      </c>
       <c r="AO91" s="1"/>
       <c r="AP91" s="1"/>
       <c r="AQ91" s="1"/>
@@ -17447,7 +17699,7 @@
         <v>2822.5</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-25.472999999999956</v>
       </c>
       <c r="M92" s="1"/>
@@ -17467,25 +17719,25 @@
         <v>700</v>
       </c>
       <c r="U92" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>559.40539999999999</v>
       </c>
       <c r="V92" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>470.84299999999979</v>
       </c>
       <c r="W92" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1030.2483999999997</v>
       </c>
-      <c r="X92" s="16"/>
-      <c r="Y92" s="16"/>
+      <c r="X92" s="1"/>
+      <c r="Y92" s="1"/>
       <c r="Z92" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11</v>
       </c>
       <c r="AA92" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.1583152397170284</v>
       </c>
       <c r="AB92" s="1">
@@ -17520,10 +17772,13 @@
       </c>
       <c r="AL92" s="1"/>
       <c r="AM92" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1030</v>
       </c>
-      <c r="AN92" s="1"/>
+      <c r="AN92" s="1">
+        <f t="shared" si="29"/>
+        <v>559.40539999999999</v>
+      </c>
       <c r="AO92" s="1"/>
       <c r="AP92" s="1"/>
       <c r="AQ92" s="1"/>
@@ -17555,7 +17810,7 @@
       <c r="J93" s="10"/>
       <c r="K93" s="10"/>
       <c r="L93" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M93" s="10"/>
@@ -17571,22 +17826,22 @@
       <c r="S93" s="10"/>
       <c r="T93" s="10"/>
       <c r="U93" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V93" s="12"/>
       <c r="W93" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA93" s="10" t="e">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X93" s="16"/>
-      <c r="Y93" s="16"/>
-      <c r="Z93" s="1" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA93" s="10" t="e">
-        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB93" s="10">
@@ -17623,10 +17878,13 @@
         <v>50</v>
       </c>
       <c r="AM93" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN93" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN93" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO93" s="1"/>
       <c r="AP93" s="1"/>
       <c r="AQ93" s="1"/>
@@ -17666,7 +17924,7 @@
         <v>3</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-3</v>
       </c>
       <c r="M94" s="1"/>
@@ -17684,30 +17942,30 @@
       <c r="S94" s="1"/>
       <c r="T94" s="1"/>
       <c r="U94" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V94" s="5">
         <v>40</v>
       </c>
       <c r="W94" s="5">
-        <f t="shared" ref="W94:W96" si="34">X94</f>
+        <f t="shared" ref="W94:W96" si="36">X94</f>
         <v>130</v>
       </c>
-      <c r="X94" s="16">
+      <c r="X94" s="1">
         <f>VLOOKUP(A94,[1]Sheet!$A:$X,23,0)</f>
         <v>130</v>
       </c>
-      <c r="Y94" s="16" t="str">
+      <c r="Y94" s="1" t="str">
         <f>VLOOKUP(A94,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка</v>
       </c>
       <c r="Z94" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA94" s="1" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB94" s="1">
@@ -17742,10 +18000,13 @@
       </c>
       <c r="AL94" s="1"/>
       <c r="AM94" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>39</v>
       </c>
-      <c r="AN94" s="1"/>
+      <c r="AN94" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO94" s="1"/>
       <c r="AP94" s="1"/>
       <c r="AQ94" s="1"/>
@@ -17783,7 +18044,7 @@
         <v>106</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-29</v>
       </c>
       <c r="M95" s="1"/>
@@ -17801,31 +18062,31 @@
         <v>68.659200000000013</v>
       </c>
       <c r="U95" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15.4</v>
       </c>
       <c r="V95" s="5">
-        <f t="shared" ref="V95" si="35">11*U95-T95-S95-R95-Q95-P95-O95-F95</f>
+        <f t="shared" ref="V95" si="37">11*U95-T95-S95-R95-Q95-P95-O95-F95</f>
         <v>54.199999999999996</v>
       </c>
       <c r="W95" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>125</v>
       </c>
-      <c r="X95" s="16">
+      <c r="X95" s="1">
         <f>VLOOKUP(A95,[1]Sheet!$A:$X,23,0)</f>
         <v>125</v>
       </c>
-      <c r="Y95" s="16" t="str">
+      <c r="Y95" s="1" t="str">
         <f>VLOOKUP(A95,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка</v>
       </c>
       <c r="Z95" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15.597402597402597</v>
       </c>
       <c r="AA95" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7.4805194805194812</v>
       </c>
       <c r="AB95" s="1">
@@ -17862,10 +18123,13 @@
         <v>141</v>
       </c>
       <c r="AM95" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>38</v>
       </c>
-      <c r="AN95" s="1"/>
+      <c r="AN95" s="1">
+        <f t="shared" si="29"/>
+        <v>4.62</v>
+      </c>
       <c r="AO95" s="1"/>
       <c r="AP95" s="1"/>
       <c r="AQ95" s="1"/>
@@ -17907,7 +18171,7 @@
         <v>41</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-23</v>
       </c>
       <c r="M96" s="1"/>
@@ -17925,30 +18189,30 @@
       </c>
       <c r="T96" s="1"/>
       <c r="U96" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3.6</v>
       </c>
       <c r="V96" s="5">
         <v>30</v>
       </c>
       <c r="W96" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>50</v>
       </c>
-      <c r="X96" s="16">
+      <c r="X96" s="1">
         <f>VLOOKUP(A96,[1]Sheet!$A:$X,23,0)</f>
         <v>50</v>
       </c>
-      <c r="Y96" s="16">
+      <c r="Y96" s="1">
         <f>VLOOKUP(A96,[1]Sheet!$A:$X,24,0)</f>
         <v>0</v>
       </c>
       <c r="Z96" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>23.333333333333332</v>
       </c>
       <c r="AA96" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>9.4444444444444446</v>
       </c>
       <c r="AB96" s="1">
@@ -17983,10 +18247,13 @@
       </c>
       <c r="AL96" s="1"/>
       <c r="AM96" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AN96" s="1"/>
+      <c r="AN96" s="1">
+        <f t="shared" si="29"/>
+        <v>0.25200000000000006</v>
+      </c>
       <c r="AO96" s="1"/>
       <c r="AP96" s="1"/>
       <c r="AQ96" s="1"/>
@@ -18030,7 +18297,7 @@
         <v>41</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M97" s="1"/>
@@ -18048,24 +18315,24 @@
       </c>
       <c r="T97" s="1"/>
       <c r="U97" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.1999999999999993</v>
       </c>
       <c r="V97" s="5">
         <v>50</v>
       </c>
       <c r="W97" s="5">
+        <f t="shared" si="26"/>
+        <v>50</v>
+      </c>
+      <c r="X97" s="1"/>
+      <c r="Y97" s="1"/>
+      <c r="Z97" s="1">
+        <f t="shared" si="27"/>
+        <v>11.097560975609756</v>
+      </c>
+      <c r="AA97" s="1">
         <f t="shared" si="25"/>
-        <v>50</v>
-      </c>
-      <c r="X97" s="16"/>
-      <c r="Y97" s="16"/>
-      <c r="Z97" s="1">
-        <f t="shared" si="26"/>
-        <v>11.097560975609756</v>
-      </c>
-      <c r="AA97" s="1">
-        <f t="shared" si="24"/>
         <v>5.0000000000000009</v>
       </c>
       <c r="AB97" s="1">
@@ -18100,10 +18367,13 @@
       </c>
       <c r="AL97" s="1"/>
       <c r="AM97" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AN97" s="1"/>
+      <c r="AN97" s="1">
+        <f t="shared" si="29"/>
+        <v>0.57399999999999995</v>
+      </c>
       <c r="AO97" s="1"/>
       <c r="AP97" s="1"/>
       <c r="AQ97" s="1"/>
@@ -18147,7 +18417,7 @@
         <v>68</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M98" s="1"/>
@@ -18163,22 +18433,22 @@
       <c r="S98" s="1"/>
       <c r="T98" s="1"/>
       <c r="U98" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>13.6</v>
       </c>
       <c r="V98" s="5"/>
       <c r="W98" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X98" s="1"/>
+      <c r="Y98" s="1"/>
+      <c r="Z98" s="1">
+        <f t="shared" si="27"/>
+        <v>11.98529411764706</v>
+      </c>
+      <c r="AA98" s="1">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X98" s="16"/>
-      <c r="Y98" s="16"/>
-      <c r="Z98" s="1">
-        <f t="shared" si="26"/>
-        <v>11.98529411764706</v>
-      </c>
-      <c r="AA98" s="1">
-        <f t="shared" si="24"/>
         <v>11.98529411764706</v>
       </c>
       <c r="AB98" s="1">
@@ -18213,10 +18483,13 @@
       </c>
       <c r="AL98" s="1"/>
       <c r="AM98" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN98" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN98" s="1">
+        <f t="shared" si="29"/>
+        <v>0.95200000000000007</v>
+      </c>
       <c r="AO98" s="1"/>
       <c r="AP98" s="1"/>
       <c r="AQ98" s="1"/>
@@ -18258,7 +18531,7 @@
         <v>23</v>
       </c>
       <c r="L99" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-26</v>
       </c>
       <c r="M99" s="10"/>
@@ -18274,22 +18547,22 @@
       <c r="S99" s="10"/>
       <c r="T99" s="10"/>
       <c r="U99" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-0.6</v>
       </c>
       <c r="V99" s="12"/>
       <c r="W99" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X99" s="1"/>
+      <c r="Y99" s="1"/>
+      <c r="Z99" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AA99" s="10">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X99" s="16"/>
-      <c r="Y99" s="16"/>
-      <c r="Z99" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AA99" s="10">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB99" s="10">
@@ -18324,10 +18597,13 @@
       </c>
       <c r="AL99" s="10"/>
       <c r="AM99" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN99" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN99" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO99" s="1"/>
       <c r="AP99" s="1"/>
       <c r="AQ99" s="1"/>
@@ -18367,7 +18643,7 @@
         <v>13</v>
       </c>
       <c r="L100" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-16</v>
       </c>
       <c r="M100" s="10"/>
@@ -18383,22 +18659,22 @@
       <c r="S100" s="10"/>
       <c r="T100" s="10"/>
       <c r="U100" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-0.6</v>
       </c>
       <c r="V100" s="12"/>
       <c r="W100" s="5">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
+      <c r="Z100" s="1">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AA100" s="10">
         <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X100" s="16"/>
-      <c r="Y100" s="16"/>
-      <c r="Z100" s="1">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AA100" s="10">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB100" s="10">
@@ -18435,10 +18711,13 @@
         <v>147</v>
       </c>
       <c r="AM100" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN100" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN100" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO100" s="1"/>
       <c r="AP100" s="1"/>
       <c r="AQ100" s="1"/>
@@ -18476,7 +18755,7 @@
         <v>91</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-14</v>
       </c>
       <c r="M101" s="1"/>
@@ -18494,7 +18773,7 @@
         <v>68.659200000000013</v>
       </c>
       <c r="U101" s="1">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15.4</v>
       </c>
       <c r="V101" s="5">
@@ -18505,20 +18784,20 @@
         <f>X101</f>
         <v>125</v>
       </c>
-      <c r="X101" s="16">
+      <c r="X101" s="1">
         <f>VLOOKUP(A101,[1]Sheet!$A:$X,23,0)</f>
         <v>125</v>
       </c>
-      <c r="Y101" s="16" t="str">
+      <c r="Y101" s="1" t="str">
         <f>VLOOKUP(A101,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка</v>
       </c>
       <c r="Z101" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15.597402597402597</v>
       </c>
       <c r="AA101" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7.4805194805194812</v>
       </c>
       <c r="AB101" s="1">
@@ -18555,10 +18834,13 @@
         <v>141</v>
       </c>
       <c r="AM101" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>38</v>
       </c>
-      <c r="AN101" s="1"/>
+      <c r="AN101" s="1">
+        <f t="shared" si="29"/>
+        <v>4.62</v>
+      </c>
       <c r="AO101" s="1"/>
       <c r="AP101" s="1"/>
       <c r="AQ101" s="1"/>
@@ -18594,7 +18876,7 @@
       <c r="J102" s="10"/>
       <c r="K102" s="10"/>
       <c r="L102" s="10">
-        <f t="shared" ref="L102:L133" si="36">E102-K102</f>
+        <f t="shared" ref="L102:L133" si="38">E102-K102</f>
         <v>0</v>
       </c>
       <c r="M102" s="10"/>
@@ -18610,22 +18892,22 @@
       <c r="S102" s="10"/>
       <c r="T102" s="10"/>
       <c r="U102" s="10">
-        <f t="shared" ref="U102:U134" si="37">E102/5</f>
+        <f t="shared" ref="U102:U134" si="39">E102/5</f>
         <v>0</v>
       </c>
       <c r="V102" s="12"/>
       <c r="W102" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X102" s="16"/>
-      <c r="Y102" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X102" s="1"/>
+      <c r="Y102" s="1"/>
       <c r="Z102" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA102" s="10" t="e">
-        <f t="shared" ref="AA102:AA134" si="38">(F102+O102+P102+Q102+R102+S102+T102)/U102</f>
+        <f t="shared" ref="AA102:AA134" si="40">(F102+O102+P102+Q102+R102+S102+T102)/U102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AB102" s="10">
@@ -18662,10 +18944,13 @@
         <v>50</v>
       </c>
       <c r="AM102" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN102" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN102" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO102" s="1"/>
       <c r="AP102" s="1"/>
       <c r="AQ102" s="1"/>
@@ -18697,7 +18982,7 @@
       <c r="J103" s="10"/>
       <c r="K103" s="10"/>
       <c r="L103" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M103" s="10"/>
@@ -18713,22 +18998,22 @@
       <c r="S103" s="10"/>
       <c r="T103" s="10"/>
       <c r="U103" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V103" s="12"/>
       <c r="W103" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X103" s="16"/>
-      <c r="Y103" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X103" s="1"/>
+      <c r="Y103" s="1"/>
       <c r="Z103" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA103" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB103" s="10">
@@ -18765,10 +19050,13 @@
         <v>50</v>
       </c>
       <c r="AM103" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN103" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN103" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO103" s="1"/>
       <c r="AP103" s="1"/>
       <c r="AQ103" s="1"/>
@@ -18800,7 +19088,7 @@
       <c r="J104" s="10"/>
       <c r="K104" s="10"/>
       <c r="L104" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M104" s="10"/>
@@ -18816,22 +19104,22 @@
       <c r="S104" s="10"/>
       <c r="T104" s="10"/>
       <c r="U104" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V104" s="12"/>
       <c r="W104" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X104" s="16"/>
-      <c r="Y104" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
       <c r="Z104" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA104" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB104" s="10">
@@ -18868,10 +19156,13 @@
         <v>50</v>
       </c>
       <c r="AM104" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN104" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN104" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO104" s="1"/>
       <c r="AP104" s="1"/>
       <c r="AQ104" s="1"/>
@@ -18915,7 +19206,7 @@
         <v>114</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2</v>
       </c>
       <c r="M105" s="1"/>
@@ -18933,7 +19224,7 @@
         <v>63.17600000000003</v>
       </c>
       <c r="U105" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>23.2</v>
       </c>
       <c r="V105" s="5"/>
@@ -18941,20 +19232,20 @@
         <f>X105</f>
         <v>100</v>
       </c>
-      <c r="X105" s="16">
+      <c r="X105" s="1">
         <f>VLOOKUP(A105,[1]Sheet!$A:$X,23,0)</f>
         <v>100</v>
       </c>
-      <c r="Y105" s="16" t="str">
+      <c r="Y105" s="1" t="str">
         <f>VLOOKUP(A105,[1]Sheet!$A:$X,24,0)</f>
         <v>Сроки хорошие.</v>
       </c>
       <c r="Z105" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>15.655172413793107</v>
       </c>
       <c r="AA105" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>11.344827586206899</v>
       </c>
       <c r="AB105" s="1">
@@ -18989,10 +19280,13 @@
       </c>
       <c r="AL105" s="1"/>
       <c r="AM105" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8</v>
       </c>
-      <c r="AN105" s="1"/>
+      <c r="AN105" s="1">
+        <f t="shared" si="29"/>
+        <v>1.8559999999999999</v>
+      </c>
       <c r="AO105" s="1"/>
       <c r="AP105" s="1"/>
       <c r="AQ105" s="1"/>
@@ -19036,7 +19330,7 @@
         <v>136</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>4</v>
       </c>
       <c r="M106" s="1"/>
@@ -19052,25 +19346,25 @@
       <c r="S106" s="1"/>
       <c r="T106" s="1"/>
       <c r="U106" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>28</v>
       </c>
       <c r="V106" s="5">
-        <f t="shared" ref="V106" si="39">11*U106-T106-S106-R106-Q106-P106-O106-F106</f>
+        <f t="shared" ref="V106" si="41">11*U106-T106-S106-R106-Q106-P106-O106-F106</f>
         <v>22.399999999999977</v>
       </c>
       <c r="W106" s="5">
         <f>V106+U106*$W$1</f>
         <v>50.399999999999977</v>
       </c>
-      <c r="X106" s="16"/>
-      <c r="Y106" s="16"/>
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
       <c r="Z106" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="AA106" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>10.200000000000001</v>
       </c>
       <c r="AB106" s="1">
@@ -19107,10 +19401,13 @@
         <v>84</v>
       </c>
       <c r="AM106" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AN106" s="1"/>
+      <c r="AN106" s="1">
+        <f t="shared" si="29"/>
+        <v>2.2400000000000002</v>
+      </c>
       <c r="AO106" s="1"/>
       <c r="AP106" s="1"/>
       <c r="AQ106" s="1"/>
@@ -19142,7 +19439,7 @@
       <c r="J107" s="10"/>
       <c r="K107" s="10"/>
       <c r="L107" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M107" s="10"/>
@@ -19158,22 +19455,22 @@
       <c r="S107" s="10"/>
       <c r="T107" s="10"/>
       <c r="U107" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V107" s="12"/>
       <c r="W107" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X107" s="16"/>
-      <c r="Y107" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X107" s="1"/>
+      <c r="Y107" s="1"/>
       <c r="Z107" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA107" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB107" s="10">
@@ -19210,10 +19507,13 @@
         <v>50</v>
       </c>
       <c r="AM107" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN107" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN107" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO107" s="1"/>
       <c r="AP107" s="1"/>
       <c r="AQ107" s="1"/>
@@ -19255,7 +19555,7 @@
         <v>150.69999999999999</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-83.407999999999987</v>
       </c>
       <c r="M108" s="1"/>
@@ -19273,30 +19573,30 @@
       <c r="S108" s="1"/>
       <c r="T108" s="1"/>
       <c r="U108" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>13.458400000000001</v>
       </c>
       <c r="V108" s="5">
         <v>100</v>
       </c>
       <c r="W108" s="5">
-        <f t="shared" ref="W108:W110" si="40">X108</f>
+        <f t="shared" ref="W108:W110" si="42">X108</f>
         <v>250</v>
       </c>
-      <c r="X108" s="16">
+      <c r="X108" s="1">
         <f>VLOOKUP(A108,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y108" s="16" t="str">
+      <c r="Y108" s="1" t="str">
         <f>VLOOKUP(A108,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250кг, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="Z108" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>25.894608571598404</v>
       </c>
       <c r="AA108" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>7.3188491945550727</v>
       </c>
       <c r="AB108" s="1">
@@ -19331,10 +19631,13 @@
       </c>
       <c r="AL108" s="1"/>
       <c r="AM108" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>250</v>
       </c>
-      <c r="AN108" s="1"/>
+      <c r="AN108" s="1">
+        <f t="shared" si="29"/>
+        <v>13.458400000000001</v>
+      </c>
       <c r="AO108" s="1"/>
       <c r="AP108" s="1"/>
       <c r="AQ108" s="1"/>
@@ -19378,7 +19681,7 @@
         <v>225.1</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-62.947000000000003</v>
       </c>
       <c r="M109" s="1"/>
@@ -19396,30 +19699,30 @@
       <c r="S109" s="1"/>
       <c r="T109" s="1"/>
       <c r="U109" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>32.430599999999998</v>
       </c>
       <c r="V109" s="5">
         <v>200</v>
       </c>
       <c r="W109" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>250</v>
       </c>
-      <c r="X109" s="16">
+      <c r="X109" s="1">
         <f>VLOOKUP(A109,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y109" s="16" t="str">
+      <c r="Y109" s="1" t="str">
         <f>VLOOKUP(A109,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250кг, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="Z109" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.162173996164116</v>
       </c>
       <c r="AA109" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3.4534051173891331</v>
       </c>
       <c r="AB109" s="1">
@@ -19454,10 +19757,13 @@
       </c>
       <c r="AL109" s="1"/>
       <c r="AM109" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>250</v>
       </c>
-      <c r="AN109" s="1"/>
+      <c r="AN109" s="1">
+        <f t="shared" si="29"/>
+        <v>32.430599999999998</v>
+      </c>
       <c r="AO109" s="1"/>
       <c r="AP109" s="1"/>
       <c r="AQ109" s="1"/>
@@ -19499,7 +19805,7 @@
         <v>68.3</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-71.855999999999995</v>
       </c>
       <c r="M110" s="1"/>
@@ -19519,30 +19825,30 @@
       </c>
       <c r="T110" s="1"/>
       <c r="U110" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.71120000000000005</v>
       </c>
       <c r="V110" s="5">
         <v>150</v>
       </c>
       <c r="W110" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>250</v>
       </c>
-      <c r="X110" s="16">
+      <c r="X110" s="1">
         <f>VLOOKUP(A110,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y110" s="16" t="str">
+      <c r="Y110" s="1" t="str">
         <f>VLOOKUP(A110,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250кг, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="Z110" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-350.11248593925757</v>
       </c>
       <c r="AA110" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.4060742407199098</v>
       </c>
       <c r="AB110" s="1">
@@ -19577,10 +19883,13 @@
       </c>
       <c r="AL110" s="1"/>
       <c r="AM110" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>250</v>
       </c>
-      <c r="AN110" s="1"/>
+      <c r="AN110" s="1">
+        <f t="shared" si="29"/>
+        <v>-0.71120000000000005</v>
+      </c>
       <c r="AO110" s="1"/>
       <c r="AP110" s="1"/>
       <c r="AQ110" s="1"/>
@@ -19612,7 +19921,7 @@
       <c r="J111" s="10"/>
       <c r="K111" s="10"/>
       <c r="L111" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M111" s="10"/>
@@ -19628,22 +19937,22 @@
       <c r="S111" s="10"/>
       <c r="T111" s="10"/>
       <c r="U111" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V111" s="12"/>
       <c r="W111" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X111" s="16"/>
-      <c r="Y111" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X111" s="1"/>
+      <c r="Y111" s="1"/>
       <c r="Z111" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA111" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB111" s="10">
@@ -19680,10 +19989,13 @@
         <v>50</v>
       </c>
       <c r="AM111" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN111" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN111" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO111" s="1"/>
       <c r="AP111" s="1"/>
       <c r="AQ111" s="1"/>
@@ -19715,7 +20027,7 @@
       <c r="J112" s="10"/>
       <c r="K112" s="10"/>
       <c r="L112" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M112" s="10"/>
@@ -19731,22 +20043,22 @@
       <c r="S112" s="10"/>
       <c r="T112" s="10"/>
       <c r="U112" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V112" s="12"/>
       <c r="W112" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X112" s="16"/>
-      <c r="Y112" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X112" s="1"/>
+      <c r="Y112" s="1"/>
       <c r="Z112" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA112" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB112" s="10">
@@ -19783,10 +20095,13 @@
         <v>50</v>
       </c>
       <c r="AM112" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN112" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN112" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO112" s="1"/>
       <c r="AP112" s="1"/>
       <c r="AQ112" s="1"/>
@@ -19828,7 +20143,7 @@
         <v>125</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-87</v>
       </c>
       <c r="M113" s="1"/>
@@ -19844,30 +20159,30 @@
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
       <c r="U113" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>7.6</v>
       </c>
       <c r="V113" s="5">
         <v>40</v>
       </c>
       <c r="W113" s="5">
-        <f t="shared" ref="W113:W115" si="41">X113</f>
+        <f t="shared" ref="W113:W115" si="43">X113</f>
         <v>250</v>
       </c>
-      <c r="X113" s="16">
+      <c r="X113" s="1">
         <f>VLOOKUP(A113,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y113" s="16" t="str">
+      <c r="Y113" s="1" t="str">
         <f>VLOOKUP(A113,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250шт, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="Z113" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>61.55263157894737</v>
       </c>
       <c r="AA113" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>28.65789473684211</v>
       </c>
       <c r="AB113" s="1">
@@ -19902,10 +20217,13 @@
       </c>
       <c r="AL113" s="1"/>
       <c r="AM113" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>70</v>
       </c>
-      <c r="AN113" s="1"/>
+      <c r="AN113" s="1">
+        <f t="shared" si="29"/>
+        <v>2.1280000000000001</v>
+      </c>
       <c r="AO113" s="1"/>
       <c r="AP113" s="1"/>
       <c r="AQ113" s="1"/>
@@ -19947,7 +20265,7 @@
         <v>128</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-67</v>
       </c>
       <c r="M114" s="1"/>
@@ -19965,30 +20283,30 @@
       <c r="S114" s="1"/>
       <c r="T114" s="1"/>
       <c r="U114" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>12.2</v>
       </c>
       <c r="V114" s="5">
         <v>100</v>
       </c>
       <c r="W114" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>250</v>
       </c>
-      <c r="X114" s="16">
+      <c r="X114" s="1">
         <f>VLOOKUP(A114,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y114" s="16" t="str">
+      <c r="Y114" s="1" t="str">
         <f>VLOOKUP(A114,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250шт, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="Z114" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>32.786885245901644</v>
       </c>
       <c r="AA114" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>12.295081967213115</v>
       </c>
       <c r="AB114" s="1">
@@ -20023,10 +20341,13 @@
       </c>
       <c r="AL114" s="1"/>
       <c r="AM114" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>70</v>
       </c>
-      <c r="AN114" s="1"/>
+      <c r="AN114" s="1">
+        <f t="shared" si="29"/>
+        <v>3.4159999999999999</v>
+      </c>
       <c r="AO114" s="1"/>
       <c r="AP114" s="1"/>
       <c r="AQ114" s="1"/>
@@ -20068,7 +20389,7 @@
         <v>99</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-46</v>
       </c>
       <c r="M115" s="1"/>
@@ -20084,28 +20405,28 @@
       <c r="S115" s="1"/>
       <c r="T115" s="1"/>
       <c r="U115" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>10.6</v>
       </c>
       <c r="V115" s="5"/>
       <c r="W115" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>250</v>
       </c>
-      <c r="X115" s="16">
+      <c r="X115" s="1">
         <f>VLOOKUP(A115,[1]Sheet!$A:$X,23,0)</f>
         <v>250</v>
       </c>
-      <c r="Y115" s="16" t="str">
+      <c r="Y115" s="1" t="str">
         <f>VLOOKUP(A115,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка, в хорошие периоды расход был 250шт, завод вроде как начал по тихоньку данные позиции отдавать поэтому прошу попробовать заказать в данном кол-ве, т.к. теряем полку по ПОЛУКОПУ.</v>
       </c>
       <c r="Z115" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>47.169811320754718</v>
       </c>
       <c r="AA115" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>23.584905660377359</v>
       </c>
       <c r="AB115" s="1">
@@ -20140,10 +20461,13 @@
       </c>
       <c r="AL115" s="1"/>
       <c r="AM115" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>70</v>
       </c>
-      <c r="AN115" s="1"/>
+      <c r="AN115" s="1">
+        <f t="shared" si="29"/>
+        <v>2.968</v>
+      </c>
       <c r="AO115" s="1"/>
       <c r="AP115" s="1"/>
       <c r="AQ115" s="1"/>
@@ -20175,7 +20499,7 @@
       <c r="J116" s="10"/>
       <c r="K116" s="10"/>
       <c r="L116" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M116" s="10"/>
@@ -20191,22 +20515,22 @@
       <c r="S116" s="10"/>
       <c r="T116" s="10"/>
       <c r="U116" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V116" s="12"/>
       <c r="W116" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X116" s="16"/>
-      <c r="Y116" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X116" s="1"/>
+      <c r="Y116" s="1"/>
       <c r="Z116" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA116" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB116" s="10">
@@ -20243,10 +20567,13 @@
         <v>50</v>
       </c>
       <c r="AM116" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN116" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN116" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO116" s="1"/>
       <c r="AP116" s="1"/>
       <c r="AQ116" s="1"/>
@@ -20290,7 +20617,7 @@
         <v>32.5</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-2.4649999999999999</v>
       </c>
       <c r="M117" s="1"/>
@@ -20306,22 +20633,22 @@
       <c r="S117" s="1"/>
       <c r="T117" s="1"/>
       <c r="U117" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>6.0069999999999997</v>
       </c>
       <c r="V117" s="5"/>
       <c r="W117" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X117" s="16"/>
-      <c r="Y117" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X117" s="1"/>
+      <c r="Y117" s="1"/>
       <c r="Z117" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12.094223406026304</v>
       </c>
       <c r="AA117" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>12.094223406026304</v>
       </c>
       <c r="AB117" s="1">
@@ -20358,10 +20685,13 @@
         <v>79</v>
       </c>
       <c r="AM117" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN117" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN117" s="1">
+        <f t="shared" si="29"/>
+        <v>6.0069999999999997</v>
+      </c>
       <c r="AO117" s="1"/>
       <c r="AP117" s="1"/>
       <c r="AQ117" s="1"/>
@@ -20405,7 +20735,7 @@
         <v>20</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-4.8999999999999488E-2</v>
       </c>
       <c r="M118" s="1"/>
@@ -20421,22 +20751,22 @@
       <c r="S118" s="1"/>
       <c r="T118" s="1"/>
       <c r="U118" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>3.9902000000000002</v>
       </c>
       <c r="V118" s="5"/>
       <c r="W118" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X118" s="16"/>
-      <c r="Y118" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X118" s="1"/>
+      <c r="Y118" s="1"/>
       <c r="Z118" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>19.850734299032631</v>
       </c>
       <c r="AA118" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>19.850734299032631</v>
       </c>
       <c r="AB118" s="1">
@@ -20473,10 +20803,13 @@
         <v>63</v>
       </c>
       <c r="AM118" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN118" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN118" s="1">
+        <f t="shared" si="29"/>
+        <v>3.9902000000000002</v>
+      </c>
       <c r="AO118" s="1"/>
       <c r="AP118" s="1"/>
       <c r="AQ118" s="1"/>
@@ -20518,7 +20851,7 @@
         <v>63</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-10</v>
       </c>
       <c r="M119" s="1"/>
@@ -20534,25 +20867,25 @@
       <c r="S119" s="1"/>
       <c r="T119" s="1"/>
       <c r="U119" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>10.6</v>
       </c>
       <c r="V119" s="5">
-        <f t="shared" ref="V119" si="42">11*U119-T119-S119-R119-Q119-P119-O119-F119</f>
+        <f t="shared" ref="V119" si="44">11*U119-T119-S119-R119-Q119-P119-O119-F119</f>
         <v>48.2</v>
       </c>
       <c r="W119" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>48.2</v>
       </c>
-      <c r="X119" s="16"/>
-      <c r="Y119" s="16"/>
+      <c r="X119" s="1"/>
+      <c r="Y119" s="1"/>
       <c r="Z119" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11</v>
       </c>
       <c r="AA119" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>6.4528301886792443</v>
       </c>
       <c r="AB119" s="1">
@@ -20589,10 +20922,13 @@
         <v>141</v>
       </c>
       <c r="AM119" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AN119" s="1"/>
+      <c r="AN119" s="1">
+        <f t="shared" si="29"/>
+        <v>0.95399999999999996</v>
+      </c>
       <c r="AO119" s="1"/>
       <c r="AP119" s="1"/>
       <c r="AQ119" s="1"/>
@@ -20624,7 +20960,7 @@
       <c r="J120" s="10"/>
       <c r="K120" s="10"/>
       <c r="L120" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="M120" s="10"/>
@@ -20640,22 +20976,22 @@
       <c r="S120" s="10"/>
       <c r="T120" s="10"/>
       <c r="U120" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V120" s="12"/>
       <c r="W120" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X120" s="16"/>
-      <c r="Y120" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X120" s="1"/>
+      <c r="Y120" s="1"/>
       <c r="Z120" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA120" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB120" s="10">
@@ -20692,10 +21028,13 @@
         <v>50</v>
       </c>
       <c r="AM120" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN120" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN120" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO120" s="1"/>
       <c r="AP120" s="1"/>
       <c r="AQ120" s="1"/>
@@ -20739,7 +21078,7 @@
         <v>124.4</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-2.4280000000000115</v>
       </c>
       <c r="M121" s="1"/>
@@ -20757,22 +21096,22 @@
         <v>63.615728799999992</v>
       </c>
       <c r="U121" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>24.394399999999997</v>
       </c>
       <c r="V121" s="5"/>
       <c r="W121" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X121" s="16"/>
-      <c r="Y121" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X121" s="1"/>
+      <c r="Y121" s="1"/>
       <c r="Z121" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16.798094316728434</v>
       </c>
       <c r="AA121" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>16.798094316728434</v>
       </c>
       <c r="AB121" s="1">
@@ -20809,10 +21148,13 @@
         <v>84</v>
       </c>
       <c r="AM121" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN121" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN121" s="1">
+        <f t="shared" si="29"/>
+        <v>24.394399999999997</v>
+      </c>
       <c r="AO121" s="1"/>
       <c r="AP121" s="1"/>
       <c r="AQ121" s="1"/>
@@ -20856,7 +21198,7 @@
         <v>220.88399999999999</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>4.5510000000000161</v>
       </c>
       <c r="M122" s="1"/>
@@ -20874,25 +21216,25 @@
         <v>106.5324968</v>
       </c>
       <c r="U122" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>45.087000000000003</v>
       </c>
       <c r="V122" s="5">
-        <f t="shared" ref="V122:V127" si="43">11*U122-T122-S122-R122-Q122-P122-O122-F122</f>
+        <f t="shared" ref="V122:V127" si="45">11*U122-T122-S122-R122-Q122-P122-O122-F122</f>
         <v>40.622200000000078</v>
       </c>
       <c r="W122" s="5">
         <f>V122+U122*$W$1</f>
         <v>85.709200000000081</v>
       </c>
-      <c r="X122" s="16"/>
-      <c r="Y122" s="16"/>
+      <c r="X122" s="1"/>
+      <c r="Y122" s="1"/>
       <c r="Z122" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12.000000000000002</v>
       </c>
       <c r="AA122" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>10.099026326879143</v>
       </c>
       <c r="AB122" s="1">
@@ -20929,10 +21271,13 @@
         <v>84</v>
       </c>
       <c r="AM122" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>86</v>
       </c>
-      <c r="AN122" s="1"/>
+      <c r="AN122" s="1">
+        <f t="shared" si="29"/>
+        <v>45.087000000000003</v>
+      </c>
       <c r="AO122" s="1"/>
       <c r="AP122" s="1"/>
       <c r="AQ122" s="1"/>
@@ -20976,7 +21321,7 @@
         <v>70.099999999999994</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3.875</v>
       </c>
       <c r="M123" s="1"/>
@@ -20994,22 +21339,22 @@
         <v>60.986176799999967</v>
       </c>
       <c r="U123" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>14.794999999999998</v>
       </c>
       <c r="V123" s="5"/>
       <c r="W123" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X123" s="16"/>
-      <c r="Y123" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X123" s="1"/>
+      <c r="Y123" s="1"/>
       <c r="Z123" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.022156133828993</v>
       </c>
       <c r="AA123" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>11.022156133828993</v>
       </c>
       <c r="AB123" s="1">
@@ -21044,10 +21389,13 @@
       </c>
       <c r="AL123" s="1"/>
       <c r="AM123" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN123" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN123" s="1">
+        <f t="shared" si="29"/>
+        <v>14.794999999999998</v>
+      </c>
       <c r="AO123" s="1"/>
       <c r="AP123" s="1"/>
       <c r="AQ123" s="1"/>
@@ -21091,7 +21439,7 @@
         <v>881.4</v>
       </c>
       <c r="L124" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>11.851999999999975</v>
       </c>
       <c r="M124" s="1"/>
@@ -21109,25 +21457,25 @@
         <v>388.36289760000011</v>
       </c>
       <c r="U124" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>178.65039999999999</v>
       </c>
       <c r="V124" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>384.25670239999999</v>
       </c>
       <c r="W124" s="5">
-        <f t="shared" ref="W124:W125" si="44">V124+U124*$W$1</f>
+        <f t="shared" ref="W124:W125" si="46">V124+U124*$W$1</f>
         <v>562.90710239999999</v>
       </c>
-      <c r="X124" s="16"/>
-      <c r="Y124" s="16"/>
+      <c r="X124" s="1"/>
+      <c r="Y124" s="1"/>
       <c r="Z124" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="AA124" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>8.8491136745285761</v>
       </c>
       <c r="AB124" s="1">
@@ -21162,10 +21510,13 @@
       </c>
       <c r="AL124" s="1"/>
       <c r="AM124" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>563</v>
       </c>
-      <c r="AN124" s="1"/>
+      <c r="AN124" s="1">
+        <f t="shared" si="29"/>
+        <v>178.65039999999999</v>
+      </c>
       <c r="AO124" s="1"/>
       <c r="AP124" s="1"/>
       <c r="AQ124" s="1"/>
@@ -21209,7 +21560,7 @@
         <v>201</v>
       </c>
       <c r="L125" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>16</v>
       </c>
       <c r="M125" s="1"/>
@@ -21225,25 +21576,25 @@
       <c r="S125" s="1"/>
       <c r="T125" s="1"/>
       <c r="U125" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>43.4</v>
       </c>
       <c r="V125" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>263</v>
       </c>
       <c r="W125" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>306.39999999999998</v>
       </c>
-      <c r="X125" s="16"/>
-      <c r="Y125" s="16"/>
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1"/>
       <c r="Z125" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="AA125" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>4.9400921658986174</v>
       </c>
       <c r="AB125" s="1">
@@ -21280,10 +21631,13 @@
         <v>84</v>
       </c>
       <c r="AM125" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>77</v>
       </c>
-      <c r="AN125" s="1"/>
+      <c r="AN125" s="1">
+        <f t="shared" si="29"/>
+        <v>10.85</v>
+      </c>
       <c r="AO125" s="1"/>
       <c r="AP125" s="1"/>
       <c r="AQ125" s="1"/>
@@ -21328,7 +21682,7 @@
         <v>133</v>
       </c>
       <c r="L126" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6</v>
       </c>
       <c r="M126" s="1"/>
@@ -21344,22 +21698,22 @@
       <c r="S126" s="1"/>
       <c r="T126" s="1"/>
       <c r="U126" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>27.8</v>
       </c>
       <c r="V126" s="5"/>
       <c r="W126" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X126" s="16"/>
-      <c r="Y126" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1"/>
       <c r="Z126" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18.417266187050359</v>
       </c>
       <c r="AA126" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>18.417266187050359</v>
       </c>
       <c r="AB126" s="1">
@@ -21396,10 +21750,13 @@
         <v>84</v>
       </c>
       <c r="AM126" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN126" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN126" s="1">
+        <f t="shared" si="29"/>
+        <v>9.0350000000000001</v>
+      </c>
       <c r="AO126" s="1"/>
       <c r="AP126" s="1"/>
       <c r="AQ126" s="1"/>
@@ -21443,7 +21800,7 @@
         <v>230</v>
       </c>
       <c r="L127" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>18</v>
       </c>
       <c r="M127" s="1"/>
@@ -21459,31 +21816,31 @@
       <c r="S127" s="1"/>
       <c r="T127" s="1"/>
       <c r="U127" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>49.6</v>
       </c>
       <c r="V127" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>192.20000000000005</v>
       </c>
       <c r="W127" s="5">
-        <f t="shared" ref="W127:W129" si="45">X127</f>
+        <f t="shared" ref="W127:W129" si="47">X127</f>
         <v>300</v>
       </c>
-      <c r="X127" s="16">
+      <c r="X127" s="1">
         <f>VLOOKUP(A127,[1]Sheet!$A:$X,23,0)</f>
         <v>300</v>
       </c>
-      <c r="Y127" s="16" t="str">
+      <c r="Y127" s="1" t="str">
         <f>VLOOKUP(A127,[1]Sheet!$A:$X,24,0)</f>
         <v>Промо, сроки большие.</v>
       </c>
       <c r="Z127" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13.173387096774196</v>
       </c>
       <c r="AA127" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>7.1250000000000009</v>
       </c>
       <c r="AB127" s="1">
@@ -21518,10 +21875,13 @@
       </c>
       <c r="AL127" s="1"/>
       <c r="AM127" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>75</v>
       </c>
-      <c r="AN127" s="1"/>
+      <c r="AN127" s="1">
+        <f t="shared" si="29"/>
+        <v>12.4</v>
+      </c>
       <c r="AO127" s="1"/>
       <c r="AP127" s="1"/>
       <c r="AQ127" s="1"/>
@@ -21559,7 +21919,7 @@
         <v>3</v>
       </c>
       <c r="L128" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-3</v>
       </c>
       <c r="M128" s="1"/>
@@ -21577,30 +21937,30 @@
       <c r="S128" s="1"/>
       <c r="T128" s="1"/>
       <c r="U128" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V128" s="5">
         <v>30</v>
       </c>
       <c r="W128" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>120</v>
       </c>
-      <c r="X128" s="16">
+      <c r="X128" s="1">
         <f>VLOOKUP(A128,[1]Sheet!$A:$X,23,0)</f>
         <v>120</v>
       </c>
-      <c r="Y128" s="16" t="str">
+      <c r="Y128" s="1" t="str">
         <f>VLOOKUP(A128,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
       <c r="Z128" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA128" s="1" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB128" s="1">
@@ -21635,10 +21995,13 @@
       </c>
       <c r="AL128" s="1"/>
       <c r="AM128" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>36</v>
       </c>
-      <c r="AN128" s="1"/>
+      <c r="AN128" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO128" s="1"/>
       <c r="AP128" s="1"/>
       <c r="AQ128" s="1"/>
@@ -21678,7 +22041,7 @@
         <v>17</v>
       </c>
       <c r="L129" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-17</v>
       </c>
       <c r="M129" s="1"/>
@@ -21698,30 +22061,30 @@
       </c>
       <c r="T129" s="1"/>
       <c r="U129" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V129" s="5">
         <v>30</v>
       </c>
       <c r="W129" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>120</v>
       </c>
-      <c r="X129" s="16">
+      <c r="X129" s="1">
         <f>VLOOKUP(A129,[1]Sheet!$A:$X,23,0)</f>
         <v>120</v>
       </c>
-      <c r="Y129" s="16" t="str">
+      <c r="Y129" s="1" t="str">
         <f>VLOOKUP(A129,[1]Sheet!$A:$X,24,0)</f>
         <v>Не хватка.</v>
       </c>
       <c r="Z129" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA129" s="1" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB129" s="1">
@@ -21758,10 +22121,13 @@
         <v>177</v>
       </c>
       <c r="AM129" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>36</v>
       </c>
-      <c r="AN129" s="1"/>
+      <c r="AN129" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO129" s="1"/>
       <c r="AP129" s="1"/>
       <c r="AQ129" s="1"/>
@@ -21805,7 +22171,7 @@
         <v>25.85</v>
       </c>
       <c r="L130" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-3.2860000000000014</v>
       </c>
       <c r="M130" s="1"/>
@@ -21821,24 +22187,24 @@
       <c r="S130" s="1"/>
       <c r="T130" s="1"/>
       <c r="U130" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>4.5128000000000004</v>
       </c>
       <c r="V130" s="5">
         <v>4</v>
       </c>
       <c r="W130" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="X130" s="16"/>
-      <c r="Y130" s="16"/>
+      <c r="X130" s="1"/>
+      <c r="Y130" s="1"/>
       <c r="Z130" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11.450363410742776</v>
       </c>
       <c r="AA130" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>10.563995745435205</v>
       </c>
       <c r="AB130" s="1">
@@ -21873,10 +22239,13 @@
       </c>
       <c r="AL130" s="1"/>
       <c r="AM130" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4</v>
       </c>
-      <c r="AN130" s="1"/>
+      <c r="AN130" s="1">
+        <f t="shared" si="29"/>
+        <v>4.5128000000000004</v>
+      </c>
       <c r="AO130" s="1"/>
       <c r="AP130" s="1"/>
       <c r="AQ130" s="1"/>
@@ -21918,7 +22287,7 @@
         <v>54</v>
       </c>
       <c r="L131" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-56</v>
       </c>
       <c r="M131" s="1"/>
@@ -21938,24 +22307,24 @@
       </c>
       <c r="T131" s="1"/>
       <c r="U131" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.4</v>
       </c>
       <c r="V131" s="5">
         <v>60</v>
       </c>
       <c r="W131" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>60</v>
       </c>
-      <c r="X131" s="16"/>
-      <c r="Y131" s="16"/>
+      <c r="X131" s="1"/>
+      <c r="Y131" s="1"/>
       <c r="Z131" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-150</v>
       </c>
       <c r="AA131" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AB131" s="1">
@@ -21990,10 +22359,13 @@
       </c>
       <c r="AL131" s="1"/>
       <c r="AM131" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>18</v>
       </c>
-      <c r="AN131" s="1"/>
+      <c r="AN131" s="1">
+        <f t="shared" si="29"/>
+        <v>-0.12</v>
+      </c>
       <c r="AO131" s="1"/>
       <c r="AP131" s="1"/>
       <c r="AQ131" s="1"/>
@@ -22035,7 +22407,7 @@
         <v>27</v>
       </c>
       <c r="L132" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-28</v>
       </c>
       <c r="M132" s="1"/>
@@ -22051,24 +22423,24 @@
       <c r="S132" s="1"/>
       <c r="T132" s="1"/>
       <c r="U132" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-0.2</v>
       </c>
       <c r="V132" s="5">
         <v>20</v>
       </c>
       <c r="W132" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="X132" s="16"/>
-      <c r="Y132" s="16"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
       <c r="Z132" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-350</v>
       </c>
       <c r="AA132" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-250</v>
       </c>
       <c r="AB132" s="1">
@@ -22103,10 +22475,13 @@
       </c>
       <c r="AL132" s="1"/>
       <c r="AM132" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2</v>
       </c>
-      <c r="AN132" s="1"/>
+      <c r="AN132" s="1">
+        <f t="shared" si="29"/>
+        <v>-2.4E-2</v>
+      </c>
       <c r="AO132" s="1"/>
       <c r="AP132" s="1"/>
       <c r="AQ132" s="1"/>
@@ -22150,7 +22525,7 @@
         <v>218</v>
       </c>
       <c r="L133" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-10</v>
       </c>
       <c r="M133" s="10"/>
@@ -22166,22 +22541,22 @@
       <c r="S133" s="10"/>
       <c r="T133" s="10"/>
       <c r="U133" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>41.6</v>
       </c>
       <c r="V133" s="12"/>
       <c r="W133" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X133" s="16"/>
-      <c r="Y133" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X133" s="1"/>
+      <c r="Y133" s="1"/>
       <c r="Z133" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.96153846153846145</v>
       </c>
       <c r="AA133" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.96153846153846145</v>
       </c>
       <c r="AB133" s="10">
@@ -22216,10 +22591,13 @@
       </c>
       <c r="AL133" s="10"/>
       <c r="AM133" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN133" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN133" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO133" s="1"/>
       <c r="AP133" s="1"/>
       <c r="AQ133" s="1"/>
@@ -22261,7 +22639,7 @@
         <v>2</v>
       </c>
       <c r="L134" s="10">
-        <f t="shared" ref="L134" si="46">E134-K134</f>
+        <f t="shared" ref="L134" si="48">E134-K134</f>
         <v>-2</v>
       </c>
       <c r="M134" s="10"/>
@@ -22277,22 +22655,22 @@
       <c r="S134" s="10"/>
       <c r="T134" s="10"/>
       <c r="U134" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V134" s="12"/>
       <c r="W134" s="5">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="X134" s="16"/>
-      <c r="Y134" s="16"/>
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="X134" s="1"/>
+      <c r="Y134" s="1"/>
       <c r="Z134" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AA134" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AB134" s="10">
@@ -22327,10 +22705,13 @@
       </c>
       <c r="AL134" s="10"/>
       <c r="AM134" s="1">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="AN134" s="1"/>
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="AN134" s="1">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
       <c r="AO134" s="1"/>
       <c r="AP134" s="1"/>
       <c r="AQ134" s="1"/>
